--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F562301-8ADD-46DD-B754-90E3222963A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DDD820-E2E4-41E7-ACC8-5DA66BB10D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="PumpDiam_tryck">Sheet1!$J$2</definedName>
     <definedName name="PumphjulsDiam">Sheet1!$B$7</definedName>
     <definedName name="PumphjulsÖppning">Sheet1!$B$8</definedName>
+    <definedName name="Qpv">Sheet1!$A$94</definedName>
     <definedName name="RörDiam_sug">Sheet1!$B$77</definedName>
     <definedName name="RörDiam_tryck">Sheet1!$B$78</definedName>
     <definedName name="RörLängd_sug">Sheet1!$E$77</definedName>
@@ -526,10 +527,10 @@
     <t>Mätserie A. Pumpprestanda finjusterade till 1200 rpm, kap 2</t>
   </si>
   <si>
-    <t>4.1 Flöde i systemet vid de två varvtalen (1200 resp 1200 rpm)</t>
-  </si>
-  <si>
     <t>Grupp 5: Emil Persson, Johan Hammar</t>
+  </si>
+  <si>
+    <t>4.1 Flöde i systemet vid de två varvtalen (1200 resp 1500 rpm)</t>
   </si>
 </sst>
 </file>
@@ -540,10 +541,10 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="175" formatCode="0.0000"/>
-    <numFmt numFmtId="176" formatCode="0.00000"/>
-    <numFmt numFmtId="178" formatCode="0.0000000"/>
-    <numFmt numFmtId="179" formatCode="0.00000000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000"/>
+    <numFmt numFmtId="170" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -745,7 +746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -870,19 +871,22 @@
     <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6773,21 +6777,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U187"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
-    <col min="2" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
+    <col min="2" max="6" width="13.33203125" style="3" customWidth="1"/>
     <col min="7" max="8" width="15" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" style="3" customWidth="1"/>
     <col min="11" max="15" width="15" style="3" customWidth="1"/>
-    <col min="16" max="20" width="11.5703125" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="3"/>
+    <col min="16" max="20" width="11.5546875" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6805,7 +6809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E2" s="5"/>
       <c r="F2" s="6" t="s">
         <v>91</v>
@@ -6827,7 +6831,7 @@
         <v>3.9126666666666664E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>64</v>
       </c>
@@ -6838,7 +6842,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
@@ -6856,7 +6860,7 @@
       <c r="J4" s="9"/>
       <c r="U4" s="10"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E5" s="5"/>
       <c r="F5" s="10" t="s">
         <v>92</v>
@@ -6875,7 +6879,7 @@
       </c>
       <c r="U5" s="5"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>59</v>
       </c>
@@ -6893,7 +6897,7 @@
       </c>
       <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>57</v>
       </c>
@@ -6916,7 +6920,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
@@ -6939,7 +6943,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>105</v>
       </c>
@@ -6963,7 +6967,7 @@
         <v>39.26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>75</v>
       </c>
@@ -6985,7 +6989,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>113</v>
       </c>
@@ -6993,7 +6997,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>2</v>
       </c>
@@ -7040,7 +7044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>5</v>
       </c>
@@ -7087,7 +7091,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -7102,7 +7106,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>15600</v>
       </c>
@@ -7158,7 +7162,7 @@
         <v>0.36379363618874272</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>14000</v>
       </c>
@@ -7214,7 +7218,7 @@
         <v>0.44116699368670792</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>13000</v>
       </c>
@@ -7270,7 +7274,7 @@
         <v>0.46205797035172885</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>11800</v>
       </c>
@@ -7326,7 +7330,7 @@
         <v>0.46705604223955755</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>9500</v>
       </c>
@@ -7382,7 +7386,7 @@
         <v>0.46269080566796272</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>8100</v>
       </c>
@@ -7438,7 +7442,7 @@
         <v>0.44636450474985923</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>7200</v>
       </c>
@@ -7494,7 +7498,7 @@
         <v>0.42159651371654927</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>6400</v>
       </c>
@@ -7550,7 +7554,7 @@
         <v>0.39753712884870851</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>5500</v>
       </c>
@@ -7606,7 +7610,7 @@
         <v>0.36539255608693993</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>4800</v>
       </c>
@@ -7662,7 +7666,7 @@
         <v>0.33749890367967239</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="19"/>
@@ -7672,7 +7676,7 @@
       <c r="K27" s="19"/>
       <c r="T27" s="22"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>88</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>2</v>
       </c>
@@ -7727,7 +7731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>5</v>
       </c>
@@ -7774,7 +7778,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -7789,7 +7793,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>12400</v>
       </c>
@@ -7848,7 +7852,7 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>11400</v>
       </c>
@@ -7907,7 +7911,7 @@
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>10500</v>
       </c>
@@ -7966,7 +7970,7 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>9600</v>
       </c>
@@ -8025,7 +8029,7 @@
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>8700</v>
       </c>
@@ -8084,7 +8088,7 @@
       <c r="Q36" s="12"/>
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>7900</v>
       </c>
@@ -8143,7 +8147,7 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>7000</v>
       </c>
@@ -8202,7 +8206,7 @@
       <c r="Q38" s="12"/>
       <c r="R38" s="12"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>6200</v>
       </c>
@@ -8258,7 +8262,7 @@
         <v>0.37992085773689571</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>5400</v>
       </c>
@@ -8314,7 +8318,7 @@
         <v>0.35188066580996941</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>4400</v>
       </c>
@@ -8370,7 +8374,7 @@
         <v>0.31117465260340577</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="24"/>
@@ -8381,7 +8385,7 @@
       <c r="L42" s="27"/>
       <c r="M42" s="28"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="24"/>
@@ -8392,7 +8396,7 @@
       <c r="L43" s="27"/>
       <c r="M43" s="28"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>114</v>
       </c>
@@ -8412,7 +8416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>2</v>
       </c>
@@ -8441,7 +8445,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>106</v>
       </c>
@@ -8459,7 +8463,7 @@
       </c>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -8482,7 +8486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A48" s="50">
         <f t="shared" ref="A48:A57" si="18">K17*1500/H17</f>
         <v>15.815560228296786</v>
@@ -8521,7 +8525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="50">
         <f t="shared" si="18"/>
         <v>14.178544636159041</v>
@@ -8549,7 +8553,7 @@
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="50">
         <f t="shared" si="18"/>
         <v>13.150007492881763</v>
@@ -8592,7 +8596,7 @@
         <v>7.5642459066536194</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="50">
         <f t="shared" si="18"/>
         <v>11.932584269662922</v>
@@ -8634,7 +8638,7 @@
         <v>7.2973299465733215</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="50">
         <f t="shared" si="18"/>
         <v>9.5737533592117057</v>
@@ -8677,7 +8681,7 @@
         <v>7.03041398649302</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="50">
         <f t="shared" si="18"/>
         <v>8.1337399583457319</v>
@@ -8720,7 +8724,7 @@
         <v>6.7634980264127211</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="50">
         <f t="shared" si="18"/>
         <v>7.2171072171072179</v>
@@ -8763,7 +8767,7 @@
         <v>6.4965820663324214</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="50">
         <f t="shared" si="18"/>
         <v>6.403794841387489</v>
@@ -8806,7 +8810,7 @@
         <v>6.2296661062521217</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
         <f t="shared" si="18"/>
         <v>5.4886162034299231</v>
@@ -8849,7 +8853,7 @@
       </c>
       <c r="M56" s="19"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="50">
         <f t="shared" si="18"/>
         <v>4.7759433962264151</v>
@@ -8893,12 +8897,12 @@
       </c>
       <c r="M57" s="19"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="19"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>68</v>
       </c>
@@ -8910,7 +8914,7 @@
       </c>
       <c r="I59" s="22"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>2</v>
       </c>
@@ -8945,7 +8949,7 @@
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
     </row>
-    <row r="61" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>106</v>
       </c>
@@ -8981,7 +8985,7 @@
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -8996,7 +9000,7 @@
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="50">
         <f>K32*1200/H32</f>
         <v>12.534631224260577</v>
@@ -9042,7 +9046,7 @@
       <c r="M63" s="30"/>
       <c r="N63" s="30"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
         <f t="shared" ref="A64:A72" si="27">K33*1200/H33</f>
         <v>11.51084517576664</v>
@@ -9088,7 +9092,7 @@
       <c r="M64" s="30"/>
       <c r="N64" s="30"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="50">
         <f t="shared" si="27"/>
         <v>10.594170403587444</v>
@@ -9133,7 +9137,7 @@
       <c r="M65" s="30"/>
       <c r="N65" s="30"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="50">
         <f t="shared" si="27"/>
         <v>9.6446511627906961</v>
@@ -9179,7 +9183,7 @@
       <c r="M66" s="30"/>
       <c r="N66" s="30"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="50">
         <f t="shared" si="27"/>
         <v>8.7502328180294278</v>
@@ -9225,7 +9229,7 @@
       <c r="M67" s="30"/>
       <c r="N67" s="30"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="50">
         <f t="shared" si="27"/>
         <v>7.9396984924623117</v>
@@ -9271,7 +9275,7 @@
       <c r="M68" s="30"/>
       <c r="N68" s="30"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="50">
         <f t="shared" si="27"/>
         <v>7.0208023774145607</v>
@@ -9316,7 +9320,7 @@
       <c r="M69" s="30"/>
       <c r="N69" s="30"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="50">
         <f t="shared" si="27"/>
         <v>6.2068965517241379</v>
@@ -9362,7 +9366,7 @@
       <c r="M70" s="30"/>
       <c r="N70" s="30"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="50">
         <f t="shared" si="27"/>
         <v>5.3960029607697999</v>
@@ -9408,7 +9412,7 @@
       <c r="M71" s="30"/>
       <c r="N71" s="30"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="50">
         <f t="shared" si="27"/>
         <v>4.3853820598006648</v>
@@ -9455,7 +9459,7 @@
       <c r="N72" s="30"/>
       <c r="O72" s="31"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="24"/>
@@ -9463,7 +9467,7 @@
       <c r="I73" s="26"/>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="19"/>
@@ -9471,16 +9475,16 @@
       <c r="I74" s="19"/>
       <c r="O74" s="5"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O75" s="5"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>67</v>
       </c>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>20</v>
       </c>
@@ -9510,7 +9514,7 @@
       </c>
       <c r="O77" s="5"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>21</v>
       </c>
@@ -9532,7 +9536,7 @@
       <c r="G78" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H78" s="7">
+      <c r="H78" s="61">
         <f>0.5+(2*0.3)+(2*1.1)</f>
         <v>3.3000000000000003</v>
       </c>
@@ -9541,7 +9545,7 @@
       </c>
       <c r="O78" s="5"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>94</v>
       </c>
@@ -9572,13 +9576,13 @@
       </c>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I80" s="4" t="s">
         <v>69</v>
       </c>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
         <v>2</v>
       </c>
@@ -9609,7 +9613,7 @@
       <c r="K81" s="5"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>106</v>
       </c>
@@ -9640,7 +9644,7 @@
       <c r="K82" s="5"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -9652,625 +9656,625 @@
       <c r="I83" s="9"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
         <v>0.01</v>
       </c>
       <c r="B84" s="36">
-        <f>(Densitet*((A84/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" ref="B84:B98" si="37">(Densitet*((A84/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
         <v>58.547434750075531</v>
       </c>
       <c r="C84" s="36">
-        <f>(Densitet*((A84/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" ref="C84:C98" si="38">(Densitet*((A84/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
         <v>70.256921700090629</v>
       </c>
       <c r="D84" s="56">
-        <f>8*((8/B84)^12+((-2.457*LN((7/B84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B84)^16)^-1.5)^(1/12)</f>
+        <f t="shared" ref="D84:D98" si="39">8*((8/B84)^12+((-2.457*LN((7/B84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B84)^16)^-1.5)^(1/12)</f>
         <v>1.0931307284973306</v>
       </c>
       <c r="E84" s="56">
-        <f>8*((8/C84)^12+((-2.457*LN((7/C84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C84)^16)^-1.5)^(1/12)</f>
+        <f t="shared" ref="E84:E98" si="40">8*((8/C84)^12+((-2.457*LN((7/C84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C84)^16)^-1.5)^(1/12)</f>
         <v>0.9109422737477757</v>
       </c>
       <c r="F84" s="59">
-        <f>D84*(RörLängd_sug/RörDiam_sug)*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" ref="F84:F98" si="41">D84*(RörLängd_sug/RörDiam_sug)*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>4.481280076578404E-6</v>
       </c>
       <c r="G84" s="58">
-        <f>E84*(RörLängd_tryck/RörDiam_tryck)*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" ref="G84:G98" si="42">E84*(RörLängd_tryck/RörDiam_tryck)*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>3.7169529467171911E-5</v>
       </c>
       <c r="H84" s="58">
-        <f>H_stat+F84+G84+Engångs_sug*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" ref="H84:H98" si="43">H_stat+F84+G84+Engångs_sug*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>2.0000423792963899</v>
       </c>
       <c r="I84" s="59">
-        <f>($H$94/$A$94^2)*A84^2</f>
+        <f>(Hpv/Qpv^2)*A84^2</f>
         <v>3.8580104312922285E-6</v>
       </c>
       <c r="K84" s="37"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
         <v>1</v>
       </c>
       <c r="B85" s="36">
-        <f>(Densitet*((A85/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>5854.7434750075527</v>
       </c>
       <c r="C85" s="36">
-        <f>(Densitet*((A85/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>7025.6921700090634</v>
       </c>
       <c r="D85" s="56">
-        <f>8*((8/B85)^12+((-2.457*LN((7/B85)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B85)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>3.8321925128009915E-2</v>
       </c>
       <c r="E85" s="56">
-        <f>8*((8/C85)^12+((-2.457*LN((7/C85)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C85)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>3.6611859393007894E-2</v>
       </c>
       <c r="F85" s="57">
-        <f>D85*(RörLängd_sug/RörDiam_sug)*(((A85/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>1.5710040445789141E-3</v>
       </c>
       <c r="G85" s="56">
-        <f>E85*(RörLängd_tryck/RörDiam_tryck)*(((A85/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.4938878409469404E-2</v>
       </c>
       <c r="H85" s="51">
-        <f>H_stat+F85+G85+Engångs_sug*(((A85/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A85/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.0237947509139773</v>
       </c>
       <c r="I85" s="56">
-        <f t="shared" ref="I85:I98" si="37">($H$94/$A$94^2)*A85^2</f>
+        <f>(Hpv/Qpv^2)*A85^2</f>
         <v>3.8580104312922282E-2</v>
       </c>
       <c r="K85" s="37"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>2</v>
       </c>
       <c r="B86" s="36">
-        <f>(Densitet*((A86/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>11709.486950015105</v>
       </c>
       <c r="C86" s="36">
-        <f>(Densitet*((A86/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>14051.384340018127</v>
       </c>
       <c r="D86" s="56">
-        <f>8*((8/B86)^12+((-2.457*LN((7/B86)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B86)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>3.2620438582158094E-2</v>
       </c>
       <c r="E86" s="56">
-        <f>8*((8/C86)^12+((-2.457*LN((7/C86)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C86)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>3.1444182088847902E-2</v>
       </c>
       <c r="F86" s="57">
-        <f>D86*(RörLängd_sug/RörDiam_sug)*(((A86/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>5.3490883641491745E-3</v>
       </c>
       <c r="G86" s="56">
-        <f>E86*(RörLängd_tryck/RörDiam_tryck)*(((A86/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>5.132116431106204E-2</v>
       </c>
       <c r="H86" s="51">
-        <f>H_stat+F86+G86+Engångs_sug*(((A86/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A86/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.0858097265149258</v>
       </c>
-      <c r="I86" s="56">
-        <f t="shared" si="37"/>
+      <c r="I86" s="51">
+        <f>(Hpv/Qpv^2)*A86^2</f>
         <v>0.15432041725168913</v>
       </c>
       <c r="K86" s="37"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>3</v>
       </c>
       <c r="B87" s="36">
-        <f>(Densitet*((A87/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>17564.230425022655</v>
       </c>
       <c r="C87" s="36">
-        <f>(Densitet*((A87/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>21077.076510027189</v>
       </c>
       <c r="D87" s="56">
-        <f>8*((8/B87)^12+((-2.457*LN((7/B87)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B87)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>3.0158934944615735E-2</v>
       </c>
       <c r="E87" s="56">
-        <f>8*((8/C87)^12+((-2.457*LN((7/C87)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C87)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.9224396022782723E-2</v>
       </c>
       <c r="F87" s="56">
-        <f>D87*(RörLängd_sug/RörDiam_sug)*(((A87/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>1.1127266638595338E-2</v>
       </c>
       <c r="G87" s="56">
-        <f>E87*(RörLängd_tryck/RörDiam_tryck)*(((A87/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.10732088875336367</v>
       </c>
       <c r="H87" s="51">
-        <f>H_stat+F87+G87+Engångs_sug*(((A87/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A87/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.1840119715313184</v>
       </c>
-      <c r="I87" s="56">
-        <f t="shared" si="37"/>
+      <c r="I87" s="51">
+        <f>(Hpv/Qpv^2)*A87^2</f>
         <v>0.34722093881630056</v>
       </c>
       <c r="K87" s="37"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="11">
         <v>4</v>
       </c>
       <c r="B88" s="36">
-        <f>(Densitet*((A88/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>23418.973900030211</v>
       </c>
       <c r="C88" s="36">
-        <f>(Densitet*((A88/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>28102.768680036253</v>
       </c>
       <c r="D88" s="56">
-        <f>8*((8/B88)^12+((-2.457*LN((7/B88)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B88)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.8728264924052185E-2</v>
       </c>
       <c r="E88" s="56">
-        <f>8*((8/C88)^12+((-2.457*LN((7/C88)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C88)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.794059197957208E-2</v>
       </c>
       <c r="F88" s="56">
-        <f>D88*(RörLängd_sug/RörDiam_sug)*(((A88/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>1.8843404234484204E-2</v>
       </c>
       <c r="G88" s="56">
-        <f>E88*(RörLängd_tryck/RörDiam_tryck)*(((A88/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.18241132275347408</v>
       </c>
       <c r="H88" s="51">
-        <f>H_stat+F88+G88+Engångs_sug*(((A88/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A88/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.317812622346819</v>
       </c>
-      <c r="I88" s="56">
-        <f t="shared" si="37"/>
+      <c r="I88" s="51">
+        <f>(Hpv/Qpv^2)*A88^2</f>
         <v>0.61728166900675652</v>
       </c>
       <c r="K88" s="37"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>5</v>
       </c>
       <c r="B89" s="36">
-        <f>(Densitet*((A89/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>29273.717375037762</v>
       </c>
       <c r="C89" s="36">
-        <f>(Densitet*((A89/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>35128.460850045311</v>
       </c>
       <c r="D89" s="56">
-        <f>8*((8/B89)^12+((-2.457*LN((7/B89)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B89)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.7775940661754841E-2</v>
       </c>
       <c r="E89" s="56">
-        <f>8*((8/C89)^12+((-2.457*LN((7/C89)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C89)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.7089706830084295E-2</v>
       </c>
       <c r="F89" s="56">
-        <f>D89*(RörLängd_sug/RörDiam_sug)*(((A89/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>2.8466807823354017E-2</v>
       </c>
       <c r="G89" s="56">
-        <f>E89*(RörLängd_tryck/RörDiam_tryck)*(((A89/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.27633794294540087</v>
       </c>
       <c r="H89" s="51">
-        <f>H_stat+F89+G89+Engångs_sug*(((A89/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A89/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.4869264622669736</v>
       </c>
-      <c r="I89" s="56">
-        <f t="shared" si="37"/>
+      <c r="I89" s="51">
+        <f>(Hpv/Qpv^2)*A89^2</f>
         <v>0.96450260782305708</v>
       </c>
       <c r="K89" s="37"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>6</v>
       </c>
       <c r="B90" s="36">
-        <f>(Densitet*((A90/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>35128.460850045311</v>
       </c>
       <c r="C90" s="36">
-        <f>(Densitet*((A90/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>42154.153020054378</v>
       </c>
       <c r="D90" s="56">
-        <f>8*((8/B90)^12+((-2.457*LN((7/B90)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B90)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.7089706830084295E-2</v>
       </c>
       <c r="E90" s="56">
-        <f>8*((8/C90)^12+((-2.457*LN((7/C90)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C90)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.6478837337398559E-2</v>
       </c>
       <c r="F90" s="56">
-        <f>D90*(RörLängd_sug/RörDiam_sug)*(((A90/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>3.9979447764091576E-2</v>
       </c>
       <c r="G90" s="56">
-        <f>E90*(RörLängd_tryck/RörDiam_tryck)*(((A90/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.3889534420475288</v>
       </c>
       <c r="H90" s="51">
-        <f>H_stat+F90+G90+Engångs_sug*(((A90/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A90/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.6911881543690566</v>
       </c>
       <c r="I90" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A90^2</f>
         <v>1.3888837552652022</v>
       </c>
       <c r="K90" s="37"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
         <v>7</v>
       </c>
       <c r="B91" s="36">
-        <f>(Densitet*((A91/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>40983.204325052866</v>
       </c>
       <c r="C91" s="36">
-        <f>(Densitet*((A91/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>49179.845190063432</v>
       </c>
       <c r="D91" s="56">
-        <f>8*((8/B91)^12+((-2.457*LN((7/B91)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B91)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.6568562047799192E-2</v>
       </c>
       <c r="E91" s="56">
-        <f>8*((8/C91)^12+((-2.457*LN((7/C91)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C91)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.6016407424642111E-2</v>
       </c>
       <c r="F91" s="56">
-        <f>D91*(RörLängd_sug/RörDiam_sug)*(((A91/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>5.3369620563667931E-2</v>
       </c>
       <c r="G91" s="56">
-        <f>E91*(RörLängd_tryck/RörDiam_tryck)*(((A91/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.52016318556239094</v>
       </c>
       <c r="H91" s="51">
-        <f>H_stat+F91+G91+Engångs_sug*(((A91/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A91/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>2.9304913606625691</v>
       </c>
       <c r="I91" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A91^2</f>
         <v>1.8904251113331918</v>
       </c>
       <c r="K91" s="37"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>8</v>
       </c>
       <c r="B92" s="36">
-        <f>(Densitet*((A92/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>46837.947800060421</v>
       </c>
       <c r="C92" s="36">
-        <f>(Densitet*((A92/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>56205.537360072507</v>
       </c>
       <c r="D92" s="56">
-        <f>8*((8/B92)^12+((-2.457*LN((7/B92)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B92)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.6157666398074673E-2</v>
       </c>
       <c r="E92" s="56">
-        <f>8*((8/C92)^12+((-2.457*LN((7/C92)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C92)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.5652817623557908E-2</v>
       </c>
       <c r="F92" s="56">
-        <f>D92*(RörLängd_sug/RörDiam_sug)*(((A92/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>6.8629203061551403E-2</v>
       </c>
       <c r="G92" s="56">
-        <f>E92*(RörLängd_tryck/RörDiam_tryck)*(((A92/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.6699019689329424</v>
       </c>
       <c r="H92" s="51">
-        <f>H_stat+F92+G92+Engångs_sug*(((A92/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A92/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>3.204762753429935</v>
       </c>
       <c r="I92" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A92^2</f>
         <v>2.4691266760270261</v>
       </c>
       <c r="K92" s="37"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="11">
         <v>9</v>
       </c>
       <c r="B93" s="36">
-        <f>(Densitet*((A93/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>52692.691275067969</v>
       </c>
       <c r="C93" s="36">
-        <f>(Densitet*((A93/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>63231.22953008156</v>
       </c>
       <c r="D93" s="56">
-        <f>8*((8/B93)^12+((-2.457*LN((7/B93)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B93)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.5824424473964859E-2</v>
       </c>
       <c r="E93" s="56">
-        <f>8*((8/C93)^12+((-2.457*LN((7/C93)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C93)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.5358659128890969E-2</v>
       </c>
       <c r="F93" s="56">
-        <f>D93*(RörLängd_sug/RörDiam_sug)*(((A93/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>8.57522759653149E-2</v>
       </c>
       <c r="G93" s="56">
-        <f>E93*(RörLängd_tryck/RörDiam_tryck)*(((A93/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>0.83812252265746989</v>
       </c>
       <c r="H93" s="51">
-        <f>H_stat+F93+G93+Engångs_sug*(((A93/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A93/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>3.5139491438770154</v>
       </c>
       <c r="I93" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A93^2</f>
         <v>3.1249884493467048</v>
       </c>
       <c r="K93" s="37"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="38">
         <v>10</v>
       </c>
       <c r="B94" s="36">
-        <f>(Densitet*((A94/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>58547.434750075525</v>
       </c>
       <c r="C94" s="36">
-        <f>(Densitet*((A94/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>70256.921700090621</v>
       </c>
       <c r="D94" s="56">
-        <f>8*((8/B94)^12+((-2.457*LN((7/B94)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B94)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.5548135310566166E-2</v>
       </c>
       <c r="E94" s="56">
-        <f>8*((8/C94)^12+((-2.457*LN((7/C94)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C94)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.5115298425681609E-2</v>
       </c>
       <c r="F94" s="56">
-        <f>D94*(RörLängd_sug/RörDiam_sug)*(((A94/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>0.1047343623011591</v>
       </c>
       <c r="G94" s="51">
-        <f>E94*(RörLängd_tryck/RörDiam_tryck)*(((A94/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.0247892229981916</v>
       </c>
       <c r="H94" s="60">
-        <f>H_stat+F94+G94+Engångs_sug*(((A94/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A94/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>3.8580104312922283</v>
       </c>
       <c r="I94" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A94^2</f>
         <v>3.8580104312922283</v>
       </c>
       <c r="K94" s="37"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="11">
         <v>11</v>
       </c>
       <c r="B95" s="36">
-        <f>(Densitet*((A95/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>64402.178225083073</v>
       </c>
       <c r="C95" s="36">
-        <f>(Densitet*((A95/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>77282.613870099696</v>
       </c>
       <c r="D95" s="56">
-        <f>8*((8/B95)^12+((-2.457*LN((7/B95)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B95)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.5314967129198923E-2</v>
       </c>
       <c r="E95" s="56">
-        <f>8*((8/C95)^12+((-2.457*LN((7/C95)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C95)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.4910312727500619E-2</v>
       </c>
       <c r="F95" s="56">
-        <f>D95*(RörLängd_sug/RörDiam_sug)*(((A95/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>0.12557197451527682</v>
       </c>
       <c r="G95" s="51">
-        <f>E95*(RörLängd_tryck/RörDiam_tryck)*(((A95/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.2298743859738575</v>
       </c>
       <c r="H95" s="51">
-        <f>H_stat+F95+G95+Engångs_sug*(((A95/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A95/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>4.2369154441405161</v>
       </c>
       <c r="I95" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A95^2</f>
         <v>4.6681926218635965</v>
       </c>
       <c r="K95" s="37"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="11">
         <v>12</v>
       </c>
       <c r="B96" s="36">
-        <f>(Densitet*((A96/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>70256.921700090621</v>
       </c>
       <c r="C96" s="36">
-        <f>(Densitet*((A96/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>84308.306040108757</v>
       </c>
       <c r="D96" s="56">
-        <f>8*((8/B96)^12+((-2.457*LN((7/B96)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B96)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.5115298425681609E-2</v>
       </c>
       <c r="E96" s="56">
-        <f>8*((8/C96)^12+((-2.457*LN((7/C96)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C96)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.4735078652284546E-2</v>
       </c>
       <c r="F96" s="56">
-        <f>D96*(RörLängd_sug/RörDiam_sug)*(((A96/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>0.14826232971617359</v>
       </c>
       <c r="G96" s="51">
-        <f>E96*(RörLängd_tryck/RörDiam_tryck)*(((A96/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.453355954951099</v>
       </c>
       <c r="H96" s="51">
-        <f>H_stat+F96+G96+Engångs_sug*(((A96/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A96/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>4.6506393428970156</v>
       </c>
       <c r="I96" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A96^2</f>
         <v>5.555535021060809</v>
       </c>
       <c r="K96" s="37"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="11">
         <v>13</v>
       </c>
       <c r="B97" s="36">
-        <f>(Densitet*((A97/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>76111.665175098169</v>
       </c>
       <c r="C97" s="36">
-        <f>(Densitet*((A97/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>91333.998210117803</v>
       </c>
       <c r="D97" s="56">
-        <f>8*((8/B97)^12+((-2.457*LN((7/B97)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B97)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.4942213741927205E-2</v>
       </c>
       <c r="E97" s="56">
-        <f>8*((8/C97)^12+((-2.457*LN((7/C97)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C97)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.4583410261233431E-2</v>
       </c>
       <c r="F97" s="56">
-        <f>D97*(RörLängd_sug/RörDiam_sug)*(((A97/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>0.17280316249756403</v>
       </c>
       <c r="G97" s="51">
-        <f>E97*(RörLängd_tryck/RörDiam_tryck)*(((A97/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.695215990262547</v>
       </c>
       <c r="H97" s="51">
-        <f>H_stat+F97+G97+Engångs_sug*(((A97/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A97/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>5.099161922488074</v>
       </c>
       <c r="I97" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A97^2</f>
         <v>6.5200376288838653</v>
       </c>
       <c r="K97" s="37"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="11">
         <v>14</v>
       </c>
       <c r="B98" s="36">
-        <f>(Densitet*((A98/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
+        <f t="shared" si="37"/>
         <v>81966.408650105732</v>
       </c>
       <c r="C98" s="36">
-        <f>(Densitet*((A98/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
+        <f t="shared" si="38"/>
         <v>98359.690380126864</v>
       </c>
       <c r="D98" s="56">
-        <f>8*((8/B98)^12+((-2.457*LN((7/B98)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B98)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="39"/>
         <v>2.4790605712953471E-2</v>
       </c>
       <c r="E98" s="56">
-        <f>8*((8/C98)^12+((-2.457*LN((7/C98)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C98)^16)^-1.5)^(1/12)</f>
+        <f t="shared" si="40"/>
         <v>2.4450747337404773E-2</v>
       </c>
       <c r="F98" s="56">
-        <f>D98*(RörLängd_sug/RörDiam_sug)*(((A98/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="41"/>
         <v>0.19919259733568023</v>
       </c>
       <c r="G98" s="51">
-        <f>E98*(RörLängd_tryck/RörDiam_tryck)*(((A98/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="42"/>
         <v>1.9554396449617522</v>
       </c>
       <c r="H98" s="51">
-        <f>H_stat+F98+G98+Engångs_sug*(((A98/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A98/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
+        <f t="shared" si="43"/>
         <v>5.5824664604434719</v>
       </c>
       <c r="I98" s="51">
-        <f t="shared" si="37"/>
+        <f>(Hpv/Qpv^2)*A98^2</f>
         <v>7.5617004453327672</v>
       </c>
       <c r="K98" s="37"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="40" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="144" s="3" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" s="3" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="41"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B150" s="9" t="s">
         <v>2</v>
       </c>
@@ -10278,7 +10282,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="B151" s="9" t="s">
         <v>106</v>
       </c>
@@ -10286,36 +10290,36 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>1200</v>
       </c>
       <c r="B153" s="44"/>
       <c r="C153" s="45"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="B154" s="44"/>
       <c r="C154" s="45"/>
     </row>
-    <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="42" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B163" s="9" t="s">
         <v>2</v>
       </c>
@@ -10323,7 +10327,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="16.2" x14ac:dyDescent="0.25">
       <c r="B164" s="9" t="s">
         <v>106</v>
       </c>
@@ -10331,7 +10335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>101</v>
       </c>
@@ -10340,7 +10344,7 @@
       <c r="D166" s="46"/>
       <c r="E166" s="9"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>96</v>
       </c>
@@ -10357,7 +10361,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>11</v>
       </c>
@@ -10374,10 +10378,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="9"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>1200</v>
       </c>
@@ -10386,7 +10390,7 @@
       <c r="D171" s="17"/>
       <c r="E171" s="17"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
         <v>1200</v>
       </c>
@@ -10395,29 +10399,29 @@
       <c r="D172" s="17"/>
       <c r="E172" s="17"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
     </row>
-    <row r="175" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C179" s="9" t="s">
         <v>78</v>
       </c>
@@ -10450,7 +10454,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C180" s="9" t="s">
         <v>81</v>
       </c>
@@ -10482,7 +10486,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" ht="16.2" x14ac:dyDescent="0.25">
       <c r="C181" s="9" t="s">
         <v>13</v>
       </c>
@@ -10514,7 +10518,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -10524,7 +10528,7 @@
       <c r="I182" s="9"/>
       <c r="J182" s="9"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>47</v>
       </c>
@@ -10537,7 +10541,7 @@
       <c r="I183" s="17"/>
       <c r="J183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>47</v>
       </c>
@@ -10550,7 +10554,7 @@
       <c r="I184" s="17"/>
       <c r="J184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>48</v>
       </c>
@@ -10563,7 +10567,7 @@
       <c r="I185" s="17"/>
       <c r="J185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>49</v>
       </c>
@@ -10576,7 +10580,7 @@
       <c r="I186" s="17"/>
       <c r="J186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>52</v>
       </c>

--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DDD820-E2E4-41E7-ACC8-5DA66BB10D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96636BE-2735-40BD-BC12-B16810D77F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="120">
   <si>
     <t>Pin</t>
   </si>
@@ -521,16 +521,25 @@
     </r>
   </si>
   <si>
-    <t>Mätserie A. Mätvärden uppmätta i vid 1200 rpm +-3%, kap 1</t>
-  </si>
-  <si>
-    <t>Mätserie A. Pumpprestanda finjusterade till 1200 rpm, kap 2</t>
-  </si>
-  <si>
     <t>Grupp 5: Emil Persson, Johan Hammar</t>
   </si>
   <si>
     <t>4.1 Flöde i systemet vid de två varvtalen (1200 resp 1500 rpm)</t>
+  </si>
+  <si>
+    <t>Mätserie A. Mätvärden uppmätta i vid 1500 rpm +-3%, kap 1</t>
+  </si>
+  <si>
+    <t>Mätserie A. Pumpprestanda finjusterade till 1500 rpm, kap 2</t>
+  </si>
+  <si>
+    <t>Svar.</t>
+  </si>
+  <si>
+    <t>Vridmomentet ökar vid högre slip. Det ser vi stämma bra översens med våran data. (Vridmoment som funktion av eftersläpning)</t>
+  </si>
+  <si>
+    <t>Affinitetslagen för uppfordringshöjd som funktion av flöde verkar fungera bäst, vi ser det då kurvorna från både finsjuterade och ändrade stämmer väl översens.</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1001,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1001,10 +1010,8 @@
             <c:v>Mätserie A</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1024,6 +1031,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$I$17:$I$26</c:f>
@@ -1102,7 +1123,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DBAF-4EE5-A983-0E39978DE3F2}"/>
@@ -1116,10 +1137,8 @@
             <c:v>Mätserie B</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1139,6 +1158,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$I$32:$I$41</c:f>
@@ -1217,7 +1250,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-ED8E-4A20-8E83-B4EB3C150E86}"/>
@@ -1498,8 +1531,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.87572437511143886"/>
           <c:y val="0.10404488586199889"/>
-          <c:w val="0.10908942435508184"/>
-          <c:h val="8.0431200163028627E-2"/>
+          <c:w val="0.12427580412330329"/>
+          <c:h val="0.15906461568606425"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1654,7 +1687,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Mätserie A: 1200 rpm</c:v>
+            <c:v>Mätserie A: 1500 rpm</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
@@ -1739,31 +1772,31 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.36379363618874266</c:v>
+                  <c:v>0.36379363618874272</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.44116699368670798</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4620579703517288</c:v>
+                  <c:v>0.46205797035172885</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.46705604223955755</c:v>
+                  <c:v>0.4670560422395576</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.46269080566796272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44636450474985923</c:v>
+                  <c:v>0.44636450474985917</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.42159651371654933</c:v>
+                  <c:v>0.42159651371654921</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.39753712884870857</c:v>
+                  <c:v>0.39753712884870845</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.36539255608693993</c:v>
+                  <c:v>0.36539255608693999</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.33749890367967239</c:v>
@@ -1867,13 +1900,13 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.35330684261725664</c:v>
+                  <c:v>0.35330684261725659</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.38077472343869462</c:v>
+                  <c:v>0.38077472343869456</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.41003342107309709</c:v>
+                  <c:v>0.4100334210730972</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.43019209347185644</c:v>
@@ -1882,16 +1915,16 @@
                   <c:v>0.42885635037256481</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.42022074112982172</c:v>
+                  <c:v>0.42022074112982183</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.39670289970810119</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.37992085773689571</c:v>
+                  <c:v>0.37992085773689577</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.35188066580996946</c:v>
+                  <c:v>0.35188066580996941</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.31117465260340582</c:v>
@@ -1995,34 +2028,34 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.35330684261725653</c:v>
+                  <c:v>0.35330684261725659</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.38077472343869462</c:v>
+                  <c:v>0.38077472343869451</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.41003342107309709</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4301920934718565</c:v>
+                  <c:v>0.43019209347185644</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42885635037256475</c:v>
+                  <c:v>0.42885635037256481</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.42022074112982177</c:v>
+                  <c:v>0.42022074112982172</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.39670289970810119</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.37992085773689566</c:v>
+                  <c:v>0.37992085773689577</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.35188066580996941</c:v>
+                  <c:v>0.35188066580996946</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.31117465260340577</c:v>
+                  <c:v>0.31117465260340582</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2455,7 +2488,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Mätserie A: 1200 rpm</c:v>
+            <c:v>Mätserie A: 1500 rpm</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
@@ -2540,34 +2573,34 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.7150694945412757</c:v>
+                  <c:v>2.752586225315953</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.6640096380168408</c:v>
+                  <c:v>3.7107374428527651</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.073127891461227</c:v>
+                  <c:v>4.1201278686292948</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.4635026767417019</c:v>
+                  <c:v>4.51365439221071</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1805966351479329</c:v>
+                  <c:v>5.2208162566808838</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.5676926564052183</c:v>
+                  <c:v>5.590884473480398</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.7108608817935247</c:v>
+                  <c:v>5.7244299008176851</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.8498306030139506</c:v>
+                  <c:v>5.8532992247767801</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.973186981911609</c:v>
+                  <c:v>5.9608237918248612</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.0003453692180724</c:v>
+                  <c:v>5.9702728835822505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2668,34 +2701,34 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.9452054144732032</c:v>
+                  <c:v>1.9663252036981085</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2599733734672474</c:v>
+                  <c:v>2.2819476845032032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5946186722645717</c:v>
+                  <c:v>2.6178887948857783</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.9118264014121946</c:v>
+                  <c:v>2.9253697800234133</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.1549971800717365</c:v>
+                  <c:v>3.173213777684369</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3072547467102695</c:v>
+                  <c:v>3.3238741172967523</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.4544938078676126</c:v>
+                  <c:v>3.4647597627201172</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.608242001526845</c:v>
+                  <c:v>3.6122556188811572</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.662264016774023</c:v>
+                  <c:v>3.6595532365987649</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.7935978686435008</c:v>
+                  <c:v>3.7809945534652827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2796,34 +2829,34 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.4315067680915039</c:v>
+                  <c:v>3.0723831307782952</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.8249667168340591</c:v>
+                  <c:v>3.5655432570362557</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2432733403307146</c:v>
+                  <c:v>4.0904512420090295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.6397830017652431</c:v>
+                  <c:v>4.5708902812865828</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.9437464750896702</c:v>
+                  <c:v>4.9581465276318264</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1340684333878368</c:v>
+                  <c:v>5.1935533082761784</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3181172598345157</c:v>
+                  <c:v>5.4136871292501807</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.5103025019085559</c:v>
+                  <c:v>5.6441494045018077</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.5778300209675287</c:v>
+                  <c:v>5.7180519321855678</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.7419973358043759</c:v>
+                  <c:v>5.9078039897895049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3369,7 +3402,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Mätserie A: 1200 rpm</c:v>
+            <c:v>Mätserie A: 1500 rpm</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
@@ -3454,34 +3487,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>316.69012611752606</c:v>
+                  <c:v>325.5026188121559</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>316.27561024564432</c:v>
+                  <c:v>324.3940953389249</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>311.71593565494709</c:v>
+                  <c:v>318.95124444332646</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>306.74174519236811</c:v>
+                  <c:v>313.67354324683527</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>289.33207857334185</c:v>
+                  <c:v>293.84198306473814</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>274.82402305748656</c:v>
+                  <c:v>277.11831025686899</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>265.29015800421024</c:v>
+                  <c:v>266.55231576139278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>256.1708088228155</c:v>
+                  <c:v>256.47468875912216</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>244.56436441013128</c:v>
+                  <c:v>243.55302267781741</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>232.12888825368395</c:v>
+                  <c:v>229.80795526139289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3582,34 +3615,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>185.70311060294719</c:v>
+                  <c:v>189.75749155312877</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>184.0450471154208</c:v>
+                  <c:v>187.64148313595405</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>180.72892014036827</c:v>
+                  <c:v>183.98523159738065</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>176.74956777030508</c:v>
+                  <c:v>178.39757347520501</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>174.09666619026299</c:v>
+                  <c:v>176.11289918584961</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>169.12247572768405</c:v>
+                  <c:v>170.82646976357563</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>165.80634875263141</c:v>
+                  <c:v>166.79328912570776</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>160.16893289504193</c:v>
+                  <c:v>160.525457955365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>152.87345354992615</c:v>
+                  <c:v>152.64722575471987</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>145.90958690231565</c:v>
+                  <c:v>144.94169844933728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3710,34 +3743,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>232.12888825368404</c:v>
+                  <c:v>370.62010068970471</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>230.05630889427601</c:v>
+                  <c:v>366.48727174991035</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>225.91115017546034</c:v>
+                  <c:v>359.3461554636342</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>220.93695971288133</c:v>
+                  <c:v>348.43276069375975</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>217.62083273782875</c:v>
+                  <c:v>343.97050622236247</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>211.40309465960505</c:v>
+                  <c:v>333.64544875698391</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>207.25793594078925</c:v>
+                  <c:v>325.76814282364779</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>200.21116611880242</c:v>
+                  <c:v>313.52628506907223</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>191.09181693740771</c:v>
+                  <c:v>298.13911280218713</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>182.38698362789458</c:v>
+                  <c:v>283.08925478386192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6356,16 +6389,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>707570</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>40824</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>207507</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>88448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>625928</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>190501</xdr:rowOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>211590</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6392,15 +6425,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>721177</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>59065</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>244927</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>130503</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>606443</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>225443</xdr:colOff>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6430,16 +6463,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>741896</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>115969</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>265646</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>68344</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>13606</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>204106</xdr:rowOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>251731</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6777,21 +6810,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U187"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="13.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="13.28515625" style="3" customWidth="1"/>
     <col min="7" max="8" width="15" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
     <col min="11" max="15" width="15" style="3" customWidth="1"/>
-    <col min="16" max="20" width="11.5546875" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9.33203125" style="3"/>
+    <col min="16" max="20" width="11.5703125" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9.28515625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6809,7 +6842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E2" s="5"/>
       <c r="F2" s="6" t="s">
         <v>91</v>
@@ -6831,7 +6864,7 @@
         <v>3.9126666666666664E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>64</v>
       </c>
@@ -6842,7 +6875,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
@@ -6860,7 +6893,7 @@
       <c r="J4" s="9"/>
       <c r="U4" s="10"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E5" s="5"/>
       <c r="F5" s="10" t="s">
         <v>92</v>
@@ -6879,7 +6912,7 @@
       </c>
       <c r="U5" s="5"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>59</v>
       </c>
@@ -6897,7 +6930,7 @@
       </c>
       <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>57</v>
       </c>
@@ -6920,7 +6953,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
@@ -6943,7 +6976,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>105</v>
       </c>
@@ -6967,7 +7000,7 @@
         <v>39.26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>75</v>
       </c>
@@ -6989,15 +7022,15 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>2</v>
       </c>
@@ -7044,7 +7077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>5</v>
       </c>
@@ -7091,7 +7124,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -7106,7 +7139,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>15600</v>
       </c>
@@ -7134,7 +7167,7 @@
         <v>1479.5555555555557</v>
       </c>
       <c r="I17" s="18">
-        <f>1-(G17/(30*2*F17))</f>
+        <f>1-(G17/(60*F17))</f>
         <v>5.3992611537368451E-2</v>
       </c>
       <c r="J17" s="51">
@@ -7162,7 +7195,7 @@
         <v>0.36379363618874272</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>14000</v>
       </c>
@@ -7190,7 +7223,7 @@
         <v>1481.1111111111111</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" ref="I18:I26" si="5">1-(G18/(30*2*F18))</f>
+        <f t="shared" ref="I18:I26" si="5">1-(G18/(60*F18))</f>
         <v>5.2998010798522399E-2</v>
       </c>
       <c r="J18" s="51">
@@ -7218,7 +7251,7 @@
         <v>0.44116699368670792</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>13000</v>
       </c>
@@ -7274,7 +7307,7 @@
         <v>0.46205797035172885</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>11800</v>
       </c>
@@ -7330,7 +7363,7 @@
         <v>0.46705604223955755</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>9500</v>
       </c>
@@ -7386,7 +7419,7 @@
         <v>0.46269080566796272</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>8100</v>
       </c>
@@ -7442,7 +7475,7 @@
         <v>0.44636450474985923</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>7200</v>
       </c>
@@ -7498,7 +7531,7 @@
         <v>0.42159651371654927</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>6400</v>
       </c>
@@ -7554,7 +7587,7 @@
         <v>0.39753712884870851</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>5500</v>
       </c>
@@ -7610,7 +7643,7 @@
         <v>0.36539255608693993</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>4800</v>
       </c>
@@ -7666,7 +7699,7 @@
         <v>0.33749890367967239</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="19"/>
@@ -7676,7 +7709,7 @@
       <c r="K27" s="19"/>
       <c r="T27" s="22"/>
     </row>
-    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>88</v>
       </c>
@@ -7684,7 +7717,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>2</v>
       </c>
@@ -7731,7 +7764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>5</v>
       </c>
@@ -7778,7 +7811,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -7793,7 +7826,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
     </row>
-    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>12400</v>
       </c>
@@ -7821,7 +7854,7 @@
         <v>1187.1111111111111</v>
       </c>
       <c r="I32" s="18">
-        <f>1-(G32/(30*2*F32))</f>
+        <f>1-(G32/(60*F32))</f>
         <v>5.1828186013489486E-2</v>
       </c>
       <c r="J32" s="51">
@@ -7852,7 +7885,7 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>11400</v>
       </c>
@@ -7880,7 +7913,7 @@
         <v>1188.4444444444446</v>
       </c>
       <c r="I33" s="18">
-        <f t="shared" ref="I33:I41" si="15">1-(G33/(30*2*F33))</f>
+        <f t="shared" ref="I33:I41" si="15">1-(G33/(60*F33))</f>
         <v>5.0763223287184855E-2</v>
       </c>
       <c r="J33" s="51">
@@ -7911,7 +7944,7 @@
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>10500</v>
       </c>
@@ -7970,7 +8003,7 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>9600</v>
       </c>
@@ -8029,7 +8062,7 @@
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>8700</v>
       </c>
@@ -8088,7 +8121,7 @@
       <c r="Q36" s="12"/>
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>7900</v>
       </c>
@@ -8147,7 +8180,7 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>7000</v>
       </c>
@@ -8206,7 +8239,7 @@
       <c r="Q38" s="12"/>
       <c r="R38" s="12"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>6200</v>
       </c>
@@ -8262,7 +8295,7 @@
         <v>0.37992085773689571</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>5400</v>
       </c>
@@ -8318,7 +8351,7 @@
         <v>0.35188066580996941</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>4400</v>
       </c>
@@ -8374,7 +8407,7 @@
         <v>0.31117465260340577</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="24"/>
@@ -8385,7 +8418,7 @@
       <c r="L42" s="27"/>
       <c r="M42" s="28"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="24"/>
@@ -8396,9 +8429,9 @@
       <c r="L43" s="27"/>
       <c r="M43" s="28"/>
     </row>
-    <row r="44" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -8416,7 +8449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>2</v>
       </c>
@@ -8445,7 +8478,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>106</v>
       </c>
@@ -8463,7 +8496,7 @@
       </c>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" spans="1:18" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -8486,26 +8519,26 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A48" s="50">
         <f t="shared" ref="A48:A57" si="18">K17*1500/H17</f>
         <v>15.815560228296786</v>
       </c>
       <c r="B48" s="51">
-        <f>L17*1500/H17</f>
-        <v>2.7150694945412757</v>
+        <f>L17*(1500/H17)^2</f>
+        <v>2.752586225315953</v>
       </c>
       <c r="C48" s="50">
-        <f>M17*1500/H17</f>
-        <v>115.20985252536632</v>
+        <f>M17*(1500/H17)^3</f>
+        <v>118.41578128663245</v>
       </c>
       <c r="D48" s="50">
-        <f>N17*1500/H17</f>
-        <v>316.69012611752606</v>
+        <f>N17*(1500/H17)^3</f>
+        <v>325.5026188121559</v>
       </c>
       <c r="E48" s="55">
         <f>C48/D48</f>
-        <v>0.36379363618874266</v>
+        <v>0.36379363618874272</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="26"/>
@@ -8525,22 +8558,22 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="50">
         <f t="shared" si="18"/>
         <v>14.178544636159041</v>
       </c>
       <c r="B49" s="51">
-        <f t="shared" ref="B49:B57" si="19">L18*1500/H18</f>
-        <v>3.6640096380168408</v>
+        <f t="shared" ref="B49:B57" si="19">L18*(1500/H18)^2</f>
+        <v>3.7107374428527651</v>
       </c>
       <c r="C49" s="50">
-        <f t="shared" ref="C49:C57" si="20">M18*1500/H18</f>
-        <v>139.53036014849988</v>
+        <f t="shared" ref="C49:C57" si="20">M18*(1500/H18)^3</f>
+        <v>143.11196781039283</v>
       </c>
       <c r="D49" s="50">
-        <f t="shared" ref="D49:D57" si="21">N18*1500/H18</f>
-        <v>316.27561024564432</v>
+        <f t="shared" ref="D49:D57" si="21">N18*(1500/H18)^3</f>
+        <v>324.3940953389249</v>
       </c>
       <c r="E49" s="55">
         <f t="shared" ref="E49:E57" si="22">C49/D49</f>
@@ -8553,26 +8586,26 @@
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="50">
         <f t="shared" si="18"/>
         <v>13.150007492881763</v>
       </c>
       <c r="B50" s="51">
         <f t="shared" si="19"/>
-        <v>4.073127891461227</v>
+        <v>4.1201278686292948</v>
       </c>
       <c r="C50" s="50">
         <f t="shared" si="20"/>
-        <v>144.03083255501494</v>
+        <v>147.37396464864156</v>
       </c>
       <c r="D50" s="50">
         <f t="shared" si="21"/>
-        <v>311.71593565494709</v>
+        <v>318.95124444332646</v>
       </c>
       <c r="E50" s="55">
         <f t="shared" si="22"/>
-        <v>0.4620579703517288</v>
+        <v>0.46205797035172885</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="19"/>
@@ -8596,26 +8629,26 @@
         <v>7.5642459066536194</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="50">
         <f t="shared" si="18"/>
         <v>11.932584269662922</v>
       </c>
       <c r="B51" s="51">
         <f t="shared" si="19"/>
-        <v>4.4635026767417019</v>
+        <v>4.51365439221071</v>
       </c>
       <c r="C51" s="50">
         <f t="shared" si="20"/>
-        <v>143.26558549920227</v>
+        <v>146.50312366412558</v>
       </c>
       <c r="D51" s="50">
         <f t="shared" si="21"/>
-        <v>306.74174519236811</v>
+        <v>313.67354324683527</v>
       </c>
       <c r="E51" s="55">
         <f t="shared" si="22"/>
-        <v>0.46705604223955755</v>
+        <v>0.4670560422395576</v>
       </c>
       <c r="F51" s="5"/>
       <c r="H51" s="11">
@@ -8638,22 +8671,22 @@
         <v>7.2973299465733215</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="50">
         <f t="shared" si="18"/>
         <v>9.5737533592117057</v>
       </c>
       <c r="B52" s="51">
         <f t="shared" si="19"/>
-        <v>5.1805966351479329</v>
+        <v>5.2208162566808838</v>
       </c>
       <c r="C52" s="50">
         <f t="shared" si="20"/>
-        <v>133.87129254068583</v>
+        <v>135.95798388329555</v>
       </c>
       <c r="D52" s="50">
         <f t="shared" si="21"/>
-        <v>289.33207857334185</v>
+        <v>293.84198306473814</v>
       </c>
       <c r="E52" s="55">
         <f t="shared" si="22"/>
@@ -8681,26 +8714,26 @@
         <v>7.03041398649302</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="50">
         <f t="shared" si="18"/>
         <v>8.1337399583457319</v>
       </c>
       <c r="B53" s="51">
         <f t="shared" si="19"/>
-        <v>5.5676926564052183</v>
+        <v>5.590884473480398</v>
       </c>
       <c r="C53" s="50">
         <f t="shared" si="20"/>
-        <v>122.67168894541888</v>
+        <v>123.69577731492515</v>
       </c>
       <c r="D53" s="50">
         <f t="shared" si="21"/>
-        <v>274.82402305748656</v>
+        <v>277.11831025686899</v>
       </c>
       <c r="E53" s="55">
         <f t="shared" si="22"/>
-        <v>0.44636450474985923</v>
+        <v>0.44636450474985917</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="19"/>
@@ -8724,26 +8757,26 @@
         <v>6.7634980264127211</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="50">
         <f t="shared" si="18"/>
         <v>7.2171072171072179</v>
       </c>
       <c r="B54" s="51">
         <f t="shared" si="19"/>
-        <v>5.7108608817935247</v>
+        <v>5.7244299008176851</v>
       </c>
       <c r="C54" s="50">
         <f t="shared" si="20"/>
-        <v>111.84540573788756</v>
+        <v>112.37752704807599</v>
       </c>
       <c r="D54" s="50">
         <f t="shared" si="21"/>
-        <v>265.29015800421024</v>
+        <v>266.55231576139278</v>
       </c>
       <c r="E54" s="55">
         <f t="shared" si="22"/>
-        <v>0.42159651371654933</v>
+        <v>0.42159651371654921</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="19"/>
@@ -8767,26 +8800,26 @@
         <v>6.4965820663324214</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="50">
         <f t="shared" si="18"/>
         <v>6.403794841387489</v>
       </c>
       <c r="B55" s="51">
         <f t="shared" si="19"/>
-        <v>5.8498306030139506</v>
+        <v>5.8532992247767801</v>
       </c>
       <c r="C55" s="50">
         <f t="shared" si="20"/>
-        <v>101.83740783427349</v>
+        <v>101.95821139166755</v>
       </c>
       <c r="D55" s="50">
         <f t="shared" si="21"/>
-        <v>256.1708088228155</v>
+        <v>256.47468875912216</v>
       </c>
       <c r="E55" s="55">
         <f t="shared" si="22"/>
-        <v>0.39753712884870857</v>
+        <v>0.39753712884870845</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="19"/>
@@ -8810,26 +8843,26 @@
         <v>6.2296661062521217</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="50">
         <f t="shared" si="18"/>
         <v>5.4886162034299231</v>
       </c>
       <c r="B56" s="51">
         <f t="shared" si="19"/>
-        <v>5.973186981911609</v>
+        <v>5.9608237918248612</v>
       </c>
       <c r="C56" s="50">
         <f t="shared" si="20"/>
-        <v>89.361998239595707</v>
+        <v>88.99246149894816</v>
       </c>
       <c r="D56" s="50">
         <f t="shared" si="21"/>
-        <v>244.56436441013128</v>
+        <v>243.55302267781741</v>
       </c>
       <c r="E56" s="55">
         <f t="shared" si="22"/>
-        <v>0.36539255608693993</v>
+        <v>0.36539255608693999</v>
       </c>
       <c r="F56" s="5"/>
       <c r="H56" s="11">
@@ -8853,22 +8886,22 @@
       </c>
       <c r="M56" s="19"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="50">
         <f t="shared" si="18"/>
         <v>4.7759433962264151</v>
       </c>
       <c r="B57" s="51">
         <f t="shared" si="19"/>
-        <v>6.0003453692180724</v>
+        <v>5.9702728835822505</v>
       </c>
       <c r="C57" s="50">
         <f t="shared" si="20"/>
-        <v>78.343245297999516</v>
+        <v>77.559932957587307</v>
       </c>
       <c r="D57" s="50">
         <f t="shared" si="21"/>
-        <v>232.12888825368395</v>
+        <v>229.80795526139289</v>
       </c>
       <c r="E57" s="55">
         <f t="shared" si="22"/>
@@ -8897,12 +8930,12 @@
       </c>
       <c r="M57" s="19"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="19"/>
     </row>
-    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>68</v>
       </c>
@@ -8914,7 +8947,7 @@
       </c>
       <c r="I59" s="22"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>2</v>
       </c>
@@ -8949,7 +8982,7 @@
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
     </row>
-    <row r="61" spans="1:14" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>106</v>
       </c>
@@ -8985,7 +9018,7 @@
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -9000,26 +9033,26 @@
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="50">
         <f>K32*1200/H32</f>
         <v>12.534631224260577</v>
       </c>
       <c r="B63" s="51">
-        <f>L32*1200/H32</f>
-        <v>1.9452054144732032</v>
+        <f>L32*(1200/H32)^2</f>
+        <v>1.9663252036981085</v>
       </c>
       <c r="C63" s="50">
-        <f>M32*1200/H32</f>
-        <v>65.610179671330471</v>
+        <f>M32*(1200/H32)^3</f>
+        <v>67.04262020360666</v>
       </c>
       <c r="D63" s="50">
-        <f>N32*1200/H32</f>
-        <v>185.70311060294719</v>
+        <f>N32*(1200/H32)^3</f>
+        <v>189.75749155312877</v>
       </c>
       <c r="E63" s="55">
         <f>C63/D63</f>
-        <v>0.35330684261725664</v>
+        <v>0.35330684261725659</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="24"/>
@@ -9028,44 +9061,44 @@
         <v>15.66828903032572</v>
       </c>
       <c r="I63" s="51">
-        <f>L32*1500/H32</f>
-        <v>2.4315067680915039</v>
+        <f>L32*(1500/H32)^2</f>
+        <v>3.0723831307782952</v>
       </c>
       <c r="J63" s="50">
-        <f>M32*1500/H32</f>
-        <v>82.012724589163071</v>
+        <f>M32*(1500/H32)^3</f>
+        <v>130.9426175851693</v>
       </c>
       <c r="K63" s="50">
-        <f>N32*1500/H32</f>
-        <v>232.12888825368404</v>
+        <f>N32*(1500/H32)^3</f>
+        <v>370.62010068970471</v>
       </c>
       <c r="L63" s="55">
         <f>J63/K63</f>
-        <v>0.35330684261725653</v>
+        <v>0.35330684261725659</v>
       </c>
       <c r="M63" s="30"/>
       <c r="N63" s="30"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="50">
         <f t="shared" ref="A64:A72" si="27">K33*1200/H33</f>
         <v>11.51084517576664</v>
       </c>
       <c r="B64" s="51">
-        <f t="shared" ref="B64:B72" si="28">L33*1200/H33</f>
-        <v>2.2599733734672474</v>
+        <f t="shared" ref="B64:B72" si="28">L33*(1200/H33)^2</f>
+        <v>2.2819476845032032</v>
       </c>
       <c r="C64" s="50">
-        <f t="shared" ref="C64:C72" si="29">M33*1200/H33</f>
-        <v>70.07970191563588</v>
+        <f t="shared" ref="C64:C72" si="29">M33*(1200/H33)^3</f>
+        <v>71.449133846719377</v>
       </c>
       <c r="D64" s="50">
-        <f t="shared" ref="D64:D72" si="30">N33*1200/H33</f>
-        <v>184.0450471154208</v>
+        <f t="shared" ref="D64:D72" si="30">N33*(1200/H33)^3</f>
+        <v>187.64148313595405</v>
       </c>
       <c r="E64" s="55">
         <f t="shared" ref="E64:E72" si="31">C64/D64</f>
-        <v>0.38077472343869462</v>
+        <v>0.38077472343869456</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="24"/>
@@ -9074,44 +9107,44 @@
         <v>14.3885564697083</v>
       </c>
       <c r="I64" s="51">
-        <f t="shared" ref="I64:I72" si="33">L33*1500/H33</f>
-        <v>2.8249667168340591</v>
+        <f t="shared" ref="I64:I72" si="33">L33*(1500/H33)^2</f>
+        <v>3.5655432570362557</v>
       </c>
       <c r="J64" s="50">
-        <f t="shared" ref="J64:J72" si="34">M33*1500/H33</f>
-        <v>87.599627394544854</v>
+        <f t="shared" ref="J64:J72" si="34">M33*(1500/H33)^3</f>
+        <v>139.5490895443738</v>
       </c>
       <c r="K64" s="50">
-        <f t="shared" ref="K64:K72" si="35">N33*1500/H33</f>
-        <v>230.05630889427601</v>
+        <f t="shared" ref="K64:K72" si="35">N33*(1500/H33)^3</f>
+        <v>366.48727174991035</v>
       </c>
       <c r="L64" s="55">
         <f t="shared" ref="L64:L72" si="36">J64/K64</f>
-        <v>0.38077472343869462</v>
+        <v>0.38077472343869451</v>
       </c>
       <c r="M64" s="30"/>
       <c r="N64" s="30"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="50">
         <f t="shared" si="27"/>
         <v>10.594170403587444</v>
       </c>
       <c r="B65" s="51">
         <f t="shared" si="28"/>
-        <v>2.5946186722645717</v>
+        <v>2.6178887948857783</v>
       </c>
       <c r="C65" s="50">
         <f t="shared" si="29"/>
-        <v>74.104897412001762</v>
+        <v>75.440093938800089</v>
       </c>
       <c r="D65" s="50">
         <f t="shared" si="30"/>
-        <v>180.72892014036827</v>
+        <v>183.98523159738065</v>
       </c>
       <c r="E65" s="55">
         <f t="shared" si="31"/>
-        <v>0.41003342107309709</v>
+        <v>0.4100334210730972</v>
       </c>
       <c r="F65" s="5"/>
       <c r="H65" s="50">
@@ -9120,15 +9153,15 @@
       </c>
       <c r="I65" s="51">
         <f t="shared" si="33"/>
-        <v>3.2432733403307146</v>
+        <v>4.0904512420090295</v>
       </c>
       <c r="J65" s="50">
         <f t="shared" si="34"/>
-        <v>92.631121765002206</v>
+        <v>147.34393347421894</v>
       </c>
       <c r="K65" s="50">
         <f t="shared" si="35"/>
-        <v>225.91115017546034</v>
+        <v>359.3461554636342</v>
       </c>
       <c r="L65" s="55">
         <f t="shared" si="36"/>
@@ -9137,22 +9170,22 @@
       <c r="M65" s="30"/>
       <c r="N65" s="30"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="50">
         <f t="shared" si="27"/>
         <v>9.6446511627906961</v>
       </c>
       <c r="B66" s="51">
         <f t="shared" si="28"/>
-        <v>2.9118264014121946</v>
+        <v>2.9253697800234133</v>
       </c>
       <c r="C66" s="50">
         <f t="shared" si="29"/>
-        <v>76.03626657935331</v>
+        <v>76.745225603597774</v>
       </c>
       <c r="D66" s="50">
         <f t="shared" si="30"/>
-        <v>176.74956777030508</v>
+        <v>178.39757347520501</v>
       </c>
       <c r="E66" s="55">
         <f t="shared" si="31"/>
@@ -9166,39 +9199,39 @@
       </c>
       <c r="I66" s="51">
         <f t="shared" si="33"/>
-        <v>3.6397830017652431</v>
+        <v>4.5708902812865828</v>
       </c>
       <c r="J66" s="50">
         <f t="shared" si="34"/>
-        <v>95.045333224191637</v>
+        <v>149.89301875702688</v>
       </c>
       <c r="K66" s="50">
         <f t="shared" si="35"/>
-        <v>220.93695971288133</v>
+        <v>348.43276069375975</v>
       </c>
       <c r="L66" s="55">
         <f t="shared" si="36"/>
-        <v>0.4301920934718565</v>
+        <v>0.43019209347185644</v>
       </c>
       <c r="M66" s="30"/>
       <c r="N66" s="30"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="50">
         <f t="shared" si="27"/>
         <v>8.7502328180294278</v>
       </c>
       <c r="B67" s="51">
         <f t="shared" si="28"/>
-        <v>3.1549971800717365</v>
+        <v>3.173213777684369</v>
       </c>
       <c r="C67" s="50">
         <f t="shared" si="29"/>
-        <v>74.662460874386881</v>
+        <v>75.527135198374907</v>
       </c>
       <c r="D67" s="50">
         <f t="shared" si="30"/>
-        <v>174.09666619026299</v>
+        <v>176.11289918584961</v>
       </c>
       <c r="E67" s="55">
         <f t="shared" si="31"/>
@@ -9212,43 +9245,43 @@
       </c>
       <c r="I67" s="51">
         <f t="shared" si="33"/>
-        <v>3.9437464750896702</v>
+        <v>4.9581465276318264</v>
       </c>
       <c r="J67" s="50">
         <f t="shared" si="34"/>
-        <v>93.328076092983594</v>
+        <v>147.51393593432596</v>
       </c>
       <c r="K67" s="50">
         <f t="shared" si="35"/>
-        <v>217.62083273782875</v>
+        <v>343.97050622236247</v>
       </c>
       <c r="L67" s="55">
         <f t="shared" si="36"/>
-        <v>0.42885635037256475</v>
+        <v>0.42885635037256481</v>
       </c>
       <c r="M67" s="30"/>
       <c r="N67" s="30"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="50">
         <f t="shared" si="27"/>
         <v>7.9396984924623117</v>
       </c>
       <c r="B68" s="51">
         <f t="shared" si="28"/>
-        <v>3.3072547467102695</v>
+        <v>3.3238741172967523</v>
       </c>
       <c r="C68" s="50">
         <f t="shared" si="29"/>
-        <v>71.068772091997673</v>
+        <v>71.784825728640854</v>
       </c>
       <c r="D68" s="50">
         <f t="shared" si="30"/>
-        <v>169.12247572768405</v>
+        <v>170.82646976357563</v>
       </c>
       <c r="E68" s="55">
         <f t="shared" si="31"/>
-        <v>0.42022074112982172</v>
+        <v>0.42022074112982183</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="24"/>
@@ -9258,39 +9291,39 @@
       </c>
       <c r="I68" s="51">
         <f t="shared" si="33"/>
-        <v>4.1340684333878368</v>
+        <v>5.1935533082761784</v>
       </c>
       <c r="J68" s="50">
         <f t="shared" si="34"/>
-        <v>88.835965114997094</v>
+        <v>140.20473775125174</v>
       </c>
       <c r="K68" s="50">
         <f t="shared" si="35"/>
-        <v>211.40309465960505</v>
+        <v>333.64544875698391</v>
       </c>
       <c r="L68" s="55">
         <f t="shared" si="36"/>
-        <v>0.42022074112982177</v>
+        <v>0.42022074112982172</v>
       </c>
       <c r="M68" s="30"/>
       <c r="N68" s="30"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="50">
         <f t="shared" si="27"/>
         <v>7.0208023774145607</v>
       </c>
       <c r="B69" s="51">
         <f t="shared" si="28"/>
-        <v>3.4544938078676126</v>
+        <v>3.4647597627201172</v>
       </c>
       <c r="C69" s="50">
         <f t="shared" si="29"/>
-        <v>65.775859340181583</v>
+        <v>66.167381448019967</v>
       </c>
       <c r="D69" s="50">
         <f t="shared" si="30"/>
-        <v>165.80634875263141</v>
+        <v>166.79328912570776</v>
       </c>
       <c r="E69" s="55">
         <f t="shared" si="31"/>
@@ -9303,15 +9336,15 @@
       </c>
       <c r="I69" s="51">
         <f t="shared" si="33"/>
-        <v>4.3181172598345157</v>
+        <v>5.4136871292501807</v>
       </c>
       <c r="J69" s="50">
         <f t="shared" si="34"/>
-        <v>82.219824175226975</v>
+        <v>129.23316689066394</v>
       </c>
       <c r="K69" s="50">
         <f t="shared" si="35"/>
-        <v>207.25793594078925</v>
+        <v>325.76814282364779</v>
       </c>
       <c r="L69" s="55">
         <f t="shared" si="36"/>
@@ -9320,26 +9353,26 @@
       <c r="M69" s="30"/>
       <c r="N69" s="30"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="50">
         <f t="shared" si="27"/>
         <v>6.2068965517241379</v>
       </c>
       <c r="B70" s="51">
         <f t="shared" si="28"/>
-        <v>3.608242001526845</v>
+        <v>3.6122556188811572</v>
       </c>
       <c r="C70" s="50">
         <f t="shared" si="29"/>
-        <v>60.851518368287621</v>
+        <v>60.986969675010265</v>
       </c>
       <c r="D70" s="50">
         <f t="shared" si="30"/>
-        <v>160.16893289504193</v>
+        <v>160.525457955365</v>
       </c>
       <c r="E70" s="55">
         <f t="shared" si="31"/>
-        <v>0.37992085773689571</v>
+        <v>0.37992085773689577</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="24"/>
@@ -9349,43 +9382,43 @@
       </c>
       <c r="I70" s="51">
         <f t="shared" si="33"/>
-        <v>4.5103025019085559</v>
+        <v>5.6441494045018077</v>
       </c>
       <c r="J70" s="50">
         <f t="shared" si="34"/>
-        <v>76.064397960359514</v>
+        <v>119.11517514650441</v>
       </c>
       <c r="K70" s="50">
         <f t="shared" si="35"/>
-        <v>200.21116611880242</v>
+        <v>313.52628506907223</v>
       </c>
       <c r="L70" s="55">
         <f t="shared" si="36"/>
-        <v>0.37992085773689566</v>
+        <v>0.37992085773689577</v>
       </c>
       <c r="M70" s="30"/>
       <c r="N70" s="30"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="50">
         <f t="shared" si="27"/>
         <v>5.3960029607697999</v>
       </c>
       <c r="B71" s="51">
         <f t="shared" si="28"/>
-        <v>3.662264016774023</v>
+        <v>3.6595532365987649</v>
       </c>
       <c r="C71" s="50">
         <f t="shared" si="29"/>
-        <v>53.793212619817453</v>
+        <v>53.713607432615539</v>
       </c>
       <c r="D71" s="50">
         <f t="shared" si="30"/>
-        <v>152.87345354992615</v>
+        <v>152.64722575471987</v>
       </c>
       <c r="E71" s="55">
         <f t="shared" si="31"/>
-        <v>0.35188066580996946</v>
+        <v>0.35188066580996941</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="24"/>
@@ -9395,39 +9428,39 @@
       </c>
       <c r="I71" s="51">
         <f t="shared" si="33"/>
-        <v>4.5778300209675287</v>
+        <v>5.7180519321855678</v>
       </c>
       <c r="J71" s="50">
         <f t="shared" si="34"/>
-        <v>67.241515774771813</v>
+        <v>104.90938951682719</v>
       </c>
       <c r="K71" s="50">
         <f t="shared" si="35"/>
-        <v>191.09181693740771</v>
+        <v>298.13911280218713</v>
       </c>
       <c r="L71" s="55">
         <f t="shared" si="36"/>
-        <v>0.35188066580996941</v>
+        <v>0.35188066580996946</v>
       </c>
       <c r="M71" s="30"/>
       <c r="N71" s="30"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="50">
         <f t="shared" si="27"/>
         <v>4.3853820598006648</v>
       </c>
       <c r="B72" s="51">
         <f t="shared" si="28"/>
-        <v>3.7935978686435008</v>
+        <v>3.7809945534652827</v>
       </c>
       <c r="C72" s="50">
         <f t="shared" si="29"/>
-        <v>45.403365015834524</v>
+        <v>45.102182662720132</v>
       </c>
       <c r="D72" s="50">
         <f t="shared" si="30"/>
-        <v>145.90958690231565</v>
+        <v>144.94169844933728</v>
       </c>
       <c r="E72" s="55">
         <f t="shared" si="31"/>
@@ -9441,25 +9474,25 @@
       </c>
       <c r="I72" s="51">
         <f t="shared" si="33"/>
-        <v>4.7419973358043759</v>
+        <v>5.9078039897895049</v>
       </c>
       <c r="J72" s="50">
         <f t="shared" si="34"/>
-        <v>56.754206269793151</v>
+        <v>88.090200513125268</v>
       </c>
       <c r="K72" s="50">
         <f t="shared" si="35"/>
-        <v>182.38698362789458</v>
+        <v>283.08925478386192</v>
       </c>
       <c r="L72" s="55">
         <f t="shared" si="36"/>
-        <v>0.31117465260340577</v>
+        <v>0.31117465260340582</v>
       </c>
       <c r="M72" s="30"/>
       <c r="N72" s="30"/>
       <c r="O72" s="31"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="24"/>
@@ -9467,7 +9500,7 @@
       <c r="I73" s="26"/>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="19"/>
@@ -9475,16 +9508,16 @@
       <c r="I74" s="19"/>
       <c r="O74" s="5"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O75" s="5"/>
     </row>
-    <row r="76" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>67</v>
       </c>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>20</v>
       </c>
@@ -9514,7 +9547,7 @@
       </c>
       <c r="O77" s="5"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>21</v>
       </c>
@@ -9545,7 +9578,7 @@
       </c>
       <c r="O78" s="5"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>94</v>
       </c>
@@ -9576,13 +9609,13 @@
       </c>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I80" s="4" t="s">
         <v>69</v>
       </c>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>2</v>
       </c>
@@ -9613,7 +9646,7 @@
       <c r="K81" s="5"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="18" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>106</v>
       </c>
@@ -9644,7 +9677,7 @@
       <c r="K82" s="5"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -9656,7 +9689,7 @@
       <c r="I83" s="9"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>0.01</v>
       </c>
@@ -9689,13 +9722,13 @@
         <v>2.0000423792963899</v>
       </c>
       <c r="I84" s="59">
-        <f>(Hpv/Qpv^2)*A84^2</f>
+        <f t="shared" ref="I84:I98" si="44">(Hpv/Qpv^2)*A84^2</f>
         <v>3.8580104312922285E-6</v>
       </c>
       <c r="K84" s="37"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
         <v>1</v>
       </c>
@@ -9728,13 +9761,13 @@
         <v>2.0237947509139773</v>
       </c>
       <c r="I85" s="56">
-        <f>(Hpv/Qpv^2)*A85^2</f>
+        <f t="shared" si="44"/>
         <v>3.8580104312922282E-2</v>
       </c>
       <c r="K85" s="37"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>2</v>
       </c>
@@ -9767,13 +9800,13 @@
         <v>2.0858097265149258</v>
       </c>
       <c r="I86" s="51">
-        <f>(Hpv/Qpv^2)*A86^2</f>
+        <f t="shared" si="44"/>
         <v>0.15432041725168913</v>
       </c>
       <c r="K86" s="37"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="11">
         <v>3</v>
       </c>
@@ -9806,13 +9839,13 @@
         <v>2.1840119715313184</v>
       </c>
       <c r="I87" s="51">
-        <f>(Hpv/Qpv^2)*A87^2</f>
+        <f t="shared" si="44"/>
         <v>0.34722093881630056</v>
       </c>
       <c r="K87" s="37"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="11">
         <v>4</v>
       </c>
@@ -9845,12 +9878,12 @@
         <v>2.317812622346819</v>
       </c>
       <c r="I88" s="51">
-        <f>(Hpv/Qpv^2)*A88^2</f>
+        <f t="shared" si="44"/>
         <v>0.61728166900675652</v>
       </c>
       <c r="K88" s="37"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="11">
         <v>5</v>
       </c>
@@ -9883,12 +9916,12 @@
         <v>2.4869264622669736</v>
       </c>
       <c r="I89" s="51">
-        <f>(Hpv/Qpv^2)*A89^2</f>
+        <f t="shared" si="44"/>
         <v>0.96450260782305708</v>
       </c>
       <c r="K89" s="37"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="11">
         <v>6</v>
       </c>
@@ -9921,12 +9954,12 @@
         <v>2.6911881543690566</v>
       </c>
       <c r="I90" s="51">
-        <f>(Hpv/Qpv^2)*A90^2</f>
+        <f t="shared" si="44"/>
         <v>1.3888837552652022</v>
       </c>
       <c r="K90" s="37"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="11">
         <v>7</v>
       </c>
@@ -9959,12 +9992,12 @@
         <v>2.9304913606625691</v>
       </c>
       <c r="I91" s="51">
-        <f>(Hpv/Qpv^2)*A91^2</f>
+        <f t="shared" si="44"/>
         <v>1.8904251113331918</v>
       </c>
       <c r="K91" s="37"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="11">
         <v>8</v>
       </c>
@@ -9997,12 +10030,12 @@
         <v>3.204762753429935</v>
       </c>
       <c r="I92" s="51">
-        <f>(Hpv/Qpv^2)*A92^2</f>
+        <f t="shared" si="44"/>
         <v>2.4691266760270261</v>
       </c>
       <c r="K92" s="37"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="11">
         <v>9</v>
       </c>
@@ -10035,12 +10068,12 @@
         <v>3.5139491438770154</v>
       </c>
       <c r="I93" s="51">
-        <f>(Hpv/Qpv^2)*A93^2</f>
+        <f t="shared" si="44"/>
         <v>3.1249884493467048</v>
       </c>
       <c r="K93" s="37"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="38">
         <v>10</v>
       </c>
@@ -10073,12 +10106,12 @@
         <v>3.8580104312922283</v>
       </c>
       <c r="I94" s="51">
-        <f>(Hpv/Qpv^2)*A94^2</f>
+        <f t="shared" si="44"/>
         <v>3.8580104312922283</v>
       </c>
       <c r="K94" s="37"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="11">
         <v>11</v>
       </c>
@@ -10111,12 +10144,12 @@
         <v>4.2369154441405161</v>
       </c>
       <c r="I95" s="51">
-        <f>(Hpv/Qpv^2)*A95^2</f>
+        <f t="shared" si="44"/>
         <v>4.6681926218635965</v>
       </c>
       <c r="K95" s="37"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="11">
         <v>12</v>
       </c>
@@ -10149,12 +10182,12 @@
         <v>4.6506393428970156</v>
       </c>
       <c r="I96" s="51">
-        <f>(Hpv/Qpv^2)*A96^2</f>
+        <f t="shared" si="44"/>
         <v>5.555535021060809</v>
       </c>
       <c r="K96" s="37"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="11">
         <v>13</v>
       </c>
@@ -10187,12 +10220,12 @@
         <v>5.099161922488074</v>
       </c>
       <c r="I97" s="51">
-        <f>(Hpv/Qpv^2)*A97^2</f>
+        <f t="shared" si="44"/>
         <v>6.5200376288838653</v>
       </c>
       <c r="K97" s="37"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="11">
         <v>14</v>
       </c>
@@ -10225,56 +10258,66 @@
         <v>5.5824664604434719</v>
       </c>
       <c r="I98" s="51">
-        <f>(Hpv/Qpv^2)*A98^2</f>
+        <f t="shared" si="44"/>
         <v>7.5617004453327672</v>
       </c>
       <c r="K98" s="37"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="40" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="144" s="3" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="69.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="43" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="41"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B150" s="9" t="s">
         <v>2</v>
       </c>
@@ -10282,7 +10325,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B151" s="9" t="s">
         <v>106</v>
       </c>
@@ -10290,36 +10333,36 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>1200</v>
       </c>
       <c r="B153" s="44"/>
       <c r="C153" s="45"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>1500</v>
       </c>
       <c r="B154" s="44"/>
       <c r="C154" s="45"/>
     </row>
-    <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="42" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B163" s="9" t="s">
         <v>2</v>
       </c>
@@ -10327,7 +10370,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="B164" s="9" t="s">
         <v>106</v>
       </c>
@@ -10335,7 +10378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>101</v>
       </c>
@@ -10344,7 +10387,7 @@
       <c r="D166" s="46"/>
       <c r="E166" s="9"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>96</v>
       </c>
@@ -10361,7 +10404,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>11</v>
       </c>
@@ -10378,10 +10421,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="9"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>1200</v>
       </c>
@@ -10390,7 +10433,7 @@
       <c r="D171" s="17"/>
       <c r="E171" s="17"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>1200</v>
       </c>
@@ -10399,29 +10442,29 @@
       <c r="D172" s="17"/>
       <c r="E172" s="17"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
     </row>
-    <row r="175" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="41" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C179" s="9" t="s">
         <v>78</v>
       </c>
@@ -10454,7 +10497,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C180" s="9" t="s">
         <v>81</v>
       </c>
@@ -10486,7 +10529,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C181" s="9" t="s">
         <v>13</v>
       </c>
@@ -10518,7 +10561,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -10528,7 +10571,7 @@
       <c r="I182" s="9"/>
       <c r="J182" s="9"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>47</v>
       </c>
@@ -10541,7 +10584,7 @@
       <c r="I183" s="17"/>
       <c r="J183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>47</v>
       </c>
@@ -10554,7 +10597,7 @@
       <c r="I184" s="17"/>
       <c r="J184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>48</v>
       </c>
@@ -10567,7 +10610,7 @@
       <c r="I185" s="17"/>
       <c r="J185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>49</v>
       </c>
@@ -10580,7 +10623,7 @@
       <c r="I186" s="17"/>
       <c r="J186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>52</v>
       </c>

--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96636BE-2735-40BD-BC12-B16810D77F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38233E01-97E0-417C-B56A-9F7A645F75CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,7 +539,7 @@
     <t>Vridmomentet ökar vid högre slip. Det ser vi stämma bra översens med våran data. (Vridmoment som funktion av eftersläpning)</t>
   </si>
   <si>
-    <t>Affinitetslagen för uppfordringshöjd som funktion av flöde verkar fungera bäst, vi ser det då kurvorna från både finsjuterade och ändrade stämmer väl översens.</t>
+    <t>Affinitetslagen för uppfordringshöjd som funktion av flöde verkar fungera bäst, vi ser det då kurvorna från både finsjuterade och ändrade stämmer väl översens. Affinitetslagen för axeleffekt som funktion av flöde fungerade sämmst då den hade störst differans mellan den finjusterade och den ändrade kurvorvna.</t>
   </si>
 </sst>
 </file>
@@ -1531,8 +1531,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.87572437511143886"/>
           <c:y val="0.10404488586199889"/>
-          <c:w val="0.12427580412330329"/>
-          <c:h val="0.15906461568606425"/>
+          <c:w val="0.12427575676103193"/>
+          <c:h val="0.16453273031638047"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4125,6 +4125,1660 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="sv-SE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Mätserie A: 1500rpm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$48:$A$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15.815560228296786</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.178544636159041</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.150007492881763</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.932584269662922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5737533592117057</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1337399583457319</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.2171072171072179</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.403794841387489</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.4886162034299231</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.7759433962264151</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$48:$B$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.752586225315953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7107374428527651</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1201278686292948</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.51365439221071</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2208162566808838</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.590884473480398</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7244299008176851</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8532992247767801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9608237918248612</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9702728835822505</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C57E-4F39-8687-4FD31864D4AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Mätserie B: 1200rpm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$63:$A$72</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>12.534631224260577</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.51084517576664</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.594170403587444</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6446511627906961</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.7502328180294278</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9396984924623117</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.0208023774145607</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.2068965517241379</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.3960029607697999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.3853820598006648</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$63:$B$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.9663252036981085</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2819476845032032</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.6178887948857783</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9253697800234133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.173213777684369</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3238741172967523</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4647597627201172</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.6122556188811572</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.6595532365987649</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C57E-4F39-8687-4FD31864D4AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Systemkurva: fiktiv</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$84:$A$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$84:$H$98</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="0.0000000">
+                  <c:v>2.0000423792963899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0237947509139773</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0858097265149258</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1840119715313184</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.317812622346819</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4869264622669736</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6911881543690566</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9304913606625691</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.204762753429935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5139491438770154</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.8580104312922283</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.2369154441405161</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.6506393428970156</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.099161922488074</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5824664604434719</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C57E-4F39-8687-4FD31864D4AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Likformskurva</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$84:$A$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$84:$I$98</c:f>
+              <c:numCache>
+                <c:formatCode>0\.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="0\.00000000">
+                  <c:v>3.8580104312922285E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8580104312922282E-2</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0\.000">
+                  <c:v>0.15432041725168913</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0\.000">
+                  <c:v>0.34722093881630056</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0\.000">
+                  <c:v>0.61728166900675652</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0\.000">
+                  <c:v>0.96450260782305708</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0\.000">
+                  <c:v>1.3888837552652022</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0\.000">
+                  <c:v>1.8904251113331918</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0\.000">
+                  <c:v>2.4691266760270261</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0\.000">
+                  <c:v>3.1249884493467048</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0\.000">
+                  <c:v>3.8580104312922283</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0\.000">
+                  <c:v>4.6681926218635965</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0\.000">
+                  <c:v>5.555535021060809</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0\.000">
+                  <c:v>6.5200376288838653</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0\.000">
+                  <c:v>7.5617004453327672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C57E-4F39-8687-4FD31864D4AE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="683165232"/>
+        <c:axId val="683174832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="683165232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683174832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="683174832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683165232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="sv-SE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="sv-SE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10092825896762905"/>
+          <c:y val="0.16708333333333336"/>
+          <c:w val="0.84284251968503932"/>
+          <c:h val="0.72088764946048411"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Mätserie A: 1500rpm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$48:$A$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15.815560228296786</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.178544636159041</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.150007492881763</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.932584269662922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5737533592117057</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1337399583457319</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.2171072171072179</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.403794841387489</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.4886162034299231</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.7759433962264151</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$48:$B$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.752586225315953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7107374428527651</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1201278686292948</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.51365439221071</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2208162566808838</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.590884473480398</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7244299008176851</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8532992247767801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9608237918248612</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.9702728835822505</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2E00-4800-8369-F172F8755577}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Mätserie B: 1200rpm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$63:$A$72</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>12.534631224260577</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.51084517576664</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.594170403587444</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6446511627906961</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.7502328180294278</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9396984924623117</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.0208023774145607</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.2068965517241379</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.3960029607697999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.3853820598006648</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$63:$B$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.9663252036981085</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2819476845032032</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.6178887948857783</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9253697800234133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.173213777684369</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3238741172967523</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4647597627201172</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.6122556188811572</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.6595532365987649</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2E00-4800-8369-F172F8755577}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Systemkurva: fiktiv</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$84:$A$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$84:$H$98</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="0.0000000">
+                  <c:v>2.0000423792963899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0237947509139773</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0858097265149258</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1840119715313184</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.317812622346819</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4869264622669736</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6911881543690566</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9304913606625691</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.204762753429935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5139491438770154</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.8580104312922283</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.2369154441405161</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.6506393428970156</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.099161922488074</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5824664604434719</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-2E00-4800-8369-F172F8755577}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Likformskurva</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$84:$A$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$84:$I$98</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="0.00000000">
+                  <c:v>3.8580104312922285E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8580104312922282E-2</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.000">
+                  <c:v>0.15432041725168913</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>0.34722093881630056</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.61728166900675652</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.96450260782305708</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>1.3888837552652022</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>1.8904251113331918</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>2.4691266760270261</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>3.1249884493467048</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.000">
+                  <c:v>3.8580104312922283</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>4.6681926218635965</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>5.555535021060809</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>6.5200376288838653</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.000">
+                  <c:v>7.5617004453327672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-2E00-4800-8369-F172F8755577}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="683165232"/>
+        <c:axId val="683174832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="683165232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="13"/>
+          <c:min val="6"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683174832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="683174832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="6"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:bevel/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683165232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="sv-SE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4285,6 +5939,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5834,6 +7568,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6494,6 +9260,80 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>484531</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>393422</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>87796</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94944A6E-56D0-1905-C94F-930AB74B5056}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>720587</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>149086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="Chart 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34D430F-BC49-4F8B-9F58-9864C8957DD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38233E01-97E0-417C-B56A-9F7A645F75CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543AB601-14E9-45E9-9C4F-468B5E78B378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="121">
   <si>
     <t>Pin</t>
   </si>
@@ -541,6 +541,9 @@
   <si>
     <t>Affinitetslagen för uppfordringshöjd som funktion av flöde verkar fungera bäst, vi ser det då kurvorna från både finsjuterade och ändrade stämmer väl översens. Affinitetslagen för axeleffekt som funktion av flöde fungerade sämmst då den hade störst differans mellan den finjusterade och den ändrade kurvorvna.</t>
   </si>
+  <si>
+    <t>Varvtalsreglering beräknat från 1500-data</t>
+  </si>
 </sst>
 </file>
 
@@ -755,7 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -896,6 +899,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4140,6 +4155,43 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="sv-SE"/>
+              <a:t>Uppfodringshöjd</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="sv-SE" baseline="0"/>
+              <a:t> som funktion av flöde</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.18926399825021872"/>
+          <c:y val="4.6296296296296294E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4687,51 +4739,51 @@
             <c:numRef>
               <c:f>Sheet1!$I$84:$I$98</c:f>
               <c:numCache>
-                <c:formatCode>0\.0000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="15"/>
-                <c:pt idx="0" formatCode="0\.00000000">
+                <c:pt idx="0" formatCode="0.00000000">
                   <c:v>3.8580104312922285E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3.8580104312922282E-2</c:v>
                 </c:pt>
-                <c:pt idx="2" formatCode="0\.000">
+                <c:pt idx="2" formatCode="0.000">
                   <c:v>0.15432041725168913</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0\.000">
+                <c:pt idx="3" formatCode="0.000">
                   <c:v>0.34722093881630056</c:v>
                 </c:pt>
-                <c:pt idx="4" formatCode="0\.000">
+                <c:pt idx="4" formatCode="0.000">
                   <c:v>0.61728166900675652</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="0\.000">
+                <c:pt idx="5" formatCode="0.000">
                   <c:v>0.96450260782305708</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0\.000">
+                <c:pt idx="6" formatCode="0.000">
                   <c:v>1.3888837552652022</c:v>
                 </c:pt>
-                <c:pt idx="7" formatCode="0\.000">
+                <c:pt idx="7" formatCode="0.000">
                   <c:v>1.8904251113331918</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0\.000">
+                <c:pt idx="8" formatCode="0.000">
                   <c:v>2.4691266760270261</c:v>
                 </c:pt>
-                <c:pt idx="9" formatCode="0\.000">
+                <c:pt idx="9" formatCode="0.000">
                   <c:v>3.1249884493467048</c:v>
                 </c:pt>
-                <c:pt idx="10" formatCode="0\.000">
+                <c:pt idx="10" formatCode="0.000">
                   <c:v>3.8580104312922283</c:v>
                 </c:pt>
-                <c:pt idx="11" formatCode="0\.000">
+                <c:pt idx="11" formatCode="0.000">
                   <c:v>4.6681926218635965</c:v>
                 </c:pt>
-                <c:pt idx="12" formatCode="0\.000">
+                <c:pt idx="12" formatCode="0.000">
                   <c:v>5.555535021060809</c:v>
                 </c:pt>
-                <c:pt idx="13" formatCode="0\.000">
+                <c:pt idx="13" formatCode="0.000">
                   <c:v>6.5200376288838653</c:v>
                 </c:pt>
-                <c:pt idx="14" formatCode="0\.000">
+                <c:pt idx="14" formatCode="0.000">
                   <c:v>7.5617004453327672</c:v>
                 </c:pt>
               </c:numCache>
@@ -4946,6 +4998,38 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="sv-SE" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Uppfodringshöjd som funktion av flöde</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9155,15 +9239,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>207507</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>88448</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>421819</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>183698</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>211590</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>330652</xdr:colOff>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9191,16 +9275,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>244927</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>130503</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>411614</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>201940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>225443</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>296880</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>197304</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9229,15 +9313,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>265646</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>68344</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>313271</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>20719</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>251731</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>204106</xdr:colOff>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>108856</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9304,15 +9388,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>720587</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>149086</xdr:rowOff>
+      <xdr:colOff>612914</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>306456</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>74544</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>49696</xdr:rowOff>
+      <xdr:colOff>115958</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>612914</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13181,15 +13265,23 @@
       <c r="A153" s="3">
         <v>1200</v>
       </c>
-      <c r="B153" s="44"/>
-      <c r="C153" s="45"/>
+      <c r="B153" s="62">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C153" s="63">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>1500</v>
       </c>
-      <c r="B154" s="44"/>
-      <c r="C154" s="45"/>
+      <c r="B154" s="62">
+        <v>11.85</v>
+      </c>
+      <c r="C154" s="63">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
     <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -13222,8 +13314,14 @@
       <c r="A166" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B166" s="44"/>
-      <c r="C166" s="45"/>
+      <c r="B166" s="44">
+        <f>Qpv</f>
+        <v>10</v>
+      </c>
+      <c r="C166" s="45">
+        <f>Hpv</f>
+        <v>3.8580104312922283</v>
+      </c>
       <c r="D166" s="46"/>
       <c r="E166" s="9"/>
     </row>
@@ -13268,19 +13366,39 @@
       <c r="A171" s="9">
         <v>1200</v>
       </c>
-      <c r="B171" s="44"/>
-      <c r="C171" s="45"/>
-      <c r="D171" s="17"/>
-      <c r="E171" s="17"/>
+      <c r="B171" s="62">
+        <v>9</v>
+      </c>
+      <c r="C171" s="63">
+        <v>3.1</v>
+      </c>
+      <c r="D171" s="64">
+        <f>A171*(B166/B171)</f>
+        <v>1333.3333333333335</v>
+      </c>
+      <c r="E171" s="64">
+        <f>A171*SQRT(C166/C171)</f>
+        <v>1338.6964074464149</v>
+      </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>1200</v>
       </c>
-      <c r="B172" s="44"/>
-      <c r="C172" s="45"/>
-      <c r="D172" s="17"/>
-      <c r="E172" s="17"/>
+      <c r="B172" s="62">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C172" s="63">
+        <v>3.25</v>
+      </c>
+      <c r="D172" s="64">
+        <f>A172*(B166/B172)</f>
+        <v>1463.4146341463418</v>
+      </c>
+      <c r="E172" s="64">
+        <f>A172*SQRT(C166/C172)</f>
+        <v>1307.4384846315459</v>
+      </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B173" s="9"/>
@@ -13415,9 +13533,16 @@
       <c r="A183" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C183" s="48"/>
-      <c r="D183" s="48"/>
-      <c r="E183" s="48"/>
+      <c r="C183" s="48">
+        <v>3.1</v>
+      </c>
+      <c r="D183" s="65">
+        <f>$B$166</f>
+        <v>10</v>
+      </c>
+      <c r="E183" s="48">
+        <v>9</v>
+      </c>
       <c r="F183" s="49"/>
       <c r="G183" s="17"/>
       <c r="H183" s="17"/>
@@ -13426,11 +13551,18 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C184" s="48"/>
-      <c r="D184" s="48"/>
-      <c r="E184" s="48"/>
+        <v>120</v>
+      </c>
+      <c r="C184" s="48">
+        <v>4.8</v>
+      </c>
+      <c r="D184" s="65">
+        <f t="shared" ref="D184:D187" si="45">$B$166</f>
+        <v>10</v>
+      </c>
+      <c r="E184" s="48">
+        <v>11.2</v>
+      </c>
       <c r="F184" s="49"/>
       <c r="G184" s="17"/>
       <c r="H184" s="17"/>
@@ -13441,9 +13573,16 @@
       <c r="A185" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C185" s="48"/>
-      <c r="D185" s="48"/>
-      <c r="E185" s="48"/>
+      <c r="C185" s="48">
+        <v>5.15</v>
+      </c>
+      <c r="D185" s="65">
+        <f t="shared" si="45"/>
+        <v>10</v>
+      </c>
+      <c r="E185" s="48">
+        <v>10</v>
+      </c>
       <c r="F185" s="49"/>
       <c r="G185" s="17"/>
       <c r="H185" s="17"/>
@@ -13454,9 +13593,16 @@
       <c r="A186" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C186" s="48"/>
-      <c r="D186" s="48"/>
-      <c r="E186" s="48"/>
+      <c r="C186" s="48">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D186" s="65">
+        <f t="shared" si="45"/>
+        <v>10</v>
+      </c>
+      <c r="E186" s="48">
+        <v>11.9</v>
+      </c>
       <c r="F186" s="49"/>
       <c r="G186" s="17"/>
       <c r="H186" s="17"/>
@@ -13467,9 +13613,16 @@
       <c r="A187" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C187" s="48"/>
-      <c r="D187" s="48"/>
-      <c r="E187" s="48"/>
+      <c r="C187" s="48">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D187" s="65">
+        <f t="shared" si="45"/>
+        <v>10</v>
+      </c>
+      <c r="E187" s="48">
+        <v>11.9</v>
+      </c>
       <c r="F187" s="49"/>
       <c r="G187" s="17"/>
       <c r="H187" s="17"/>

--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543AB601-14E9-45E9-9C4F-468B5E78B378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5112D32-B519-455D-9B94-05834A59BB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -758,7 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -794,9 +794,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -910,7 +907,7 @@
     <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9822,16 +9819,16 @@
       <c r="F5" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="52">
         <v>179</v>
       </c>
-      <c r="H5" s="53">
+      <c r="H5" s="52">
         <v>136</v>
       </c>
-      <c r="I5" s="53">
+      <c r="I5" s="52">
         <v>60.9</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="53">
         <v>39.22</v>
       </c>
       <c r="U5" s="5"/>
@@ -9840,16 +9837,16 @@
       <c r="A6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="52">
         <v>179</v>
       </c>
-      <c r="H6" s="53">
+      <c r="H6" s="52">
         <v>142</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="52">
         <v>61.1</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="53">
         <v>39.119999999999997</v>
       </c>
       <c r="U6" s="5"/>
@@ -9864,16 +9861,16 @@
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="52">
         <v>180</v>
       </c>
-      <c r="H7" s="53">
+      <c r="H7" s="52">
         <v>135</v>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="52">
         <v>60.9</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="53">
         <v>38.96</v>
       </c>
     </row>
@@ -9887,16 +9884,16 @@
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="52">
         <v>179.5</v>
       </c>
-      <c r="H8" s="53">
+      <c r="H8" s="52">
         <v>136.5</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="52">
         <v>61.09</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="53">
         <v>39.1</v>
       </c>
     </row>
@@ -9911,16 +9908,16 @@
         <v>62</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="53">
+      <c r="G9" s="52">
         <v>179.5</v>
       </c>
-      <c r="H9" s="53">
+      <c r="H9" s="52">
         <v>137</v>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="52">
         <v>60.8</v>
       </c>
-      <c r="J9" s="54">
+      <c r="J9" s="53">
         <v>39.26</v>
       </c>
     </row>
@@ -9933,16 +9930,16 @@
         <v>3.1415926535897931</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="53">
+      <c r="G10" s="52">
         <v>179</v>
       </c>
-      <c r="H10" s="53">
+      <c r="H10" s="52">
         <v>137</v>
       </c>
-      <c r="I10" s="53">
+      <c r="I10" s="52">
         <v>60.8</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="53">
         <v>39.1</v>
       </c>
     </row>
@@ -10067,7 +10064,7 @@
       <c r="A17" s="11">
         <v>15600</v>
       </c>
-      <c r="B17" s="53">
+      <c r="B17" s="52">
         <v>-5</v>
       </c>
       <c r="C17" s="11">
@@ -10082,39 +10079,39 @@
       <c r="F17" s="11">
         <v>39.1</v>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="49">
         <f>D17/3</f>
         <v>2219.3333333333335</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="49">
         <f>G17/1.5</f>
         <v>1479.5555555555557</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="17">
         <f>1-(G17/(60*F17))</f>
         <v>5.3992611537368451E-2</v>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="50">
         <f>((E17/1000)*Tyngdacc)*Hävarm</f>
         <v>1.3440746400000003</v>
       </c>
-      <c r="K17" s="50">
+      <c r="K17" s="49">
         <f>A17/1000</f>
         <v>15.6</v>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="50">
         <f t="shared" ref="L17:L26" si="0">delta_z+((C17-ABS(B17/10))*1000/(Densitet*Tyngdacc))+(((4*(K17/3600))/(π*PumpDiam_tryck^2))^2-((4*(K17/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
         <v>2.6780641029119727</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="49">
         <f t="shared" ref="M17:M26" si="1">Densitet*Tyngdacc*(K17/3600)*L17</f>
         <v>113.63958490576134</v>
       </c>
-      <c r="N17" s="50">
+      <c r="N17" s="49">
         <f t="shared" ref="N17:N26" si="2">((G17*2*π)/60)*J17</f>
         <v>312.37375699118348</v>
       </c>
-      <c r="O17" s="55">
+      <c r="O17" s="54">
         <f>M17/N17</f>
         <v>0.36379363618874272</v>
       </c>
@@ -10123,7 +10120,7 @@
       <c r="A18" s="11">
         <v>14000</v>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="52">
         <v>2.5</v>
       </c>
       <c r="C18" s="11">
@@ -10138,39 +10135,39 @@
       <c r="F18" s="11">
         <v>39.1</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="49">
         <f t="shared" ref="G18:G26" si="3">D18/3</f>
         <v>2221.6666666666665</v>
       </c>
-      <c r="H18" s="50">
+      <c r="H18" s="49">
         <f t="shared" ref="H18:H26" si="4">G18/1.5</f>
         <v>1481.1111111111111</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <f t="shared" ref="I18:I26" si="5">1-(G18/(60*F18))</f>
         <v>5.2998010798522399E-2</v>
       </c>
-      <c r="J18" s="51">
+      <c r="J18" s="50">
         <f t="shared" ref="J18:J26" si="6">((E18/1000)*Tyngdacc)*Hävarm</f>
         <v>1.3423153800000001</v>
       </c>
-      <c r="K18" s="50">
+      <c r="K18" s="49">
         <f t="shared" ref="K18:K26" si="7">A18/1000</f>
         <v>14</v>
       </c>
-      <c r="L18" s="51">
+      <c r="L18" s="50">
         <f t="shared" si="0"/>
         <v>3.6178702573899622</v>
       </c>
-      <c r="M18" s="50">
+      <c r="M18" s="49">
         <f t="shared" si="1"/>
         <v>137.7733111688521</v>
       </c>
-      <c r="N18" s="50">
+      <c r="N18" s="49">
         <f t="shared" si="2"/>
         <v>312.29288033884734</v>
       </c>
-      <c r="O18" s="55">
+      <c r="O18" s="54">
         <f t="shared" ref="O18:O26" si="8">M18/N18</f>
         <v>0.44116699368670792</v>
       </c>
@@ -10179,7 +10176,7 @@
       <c r="A19" s="11">
         <v>13000</v>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="52">
         <v>6.5</v>
       </c>
       <c r="C19" s="11">
@@ -10194,39 +10191,39 @@
       <c r="F19" s="11">
         <v>39.1</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="49">
         <f>D19/3</f>
         <v>2224.3333333333335</v>
       </c>
-      <c r="H19" s="50">
+      <c r="H19" s="49">
         <f t="shared" si="4"/>
         <v>1482.8888888888889</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="17">
         <f t="shared" si="5"/>
         <v>5.18613242398408E-2</v>
       </c>
-      <c r="J19" s="51">
+      <c r="J19" s="50">
         <f t="shared" si="6"/>
         <v>1.3229635200000003</v>
       </c>
-      <c r="K19" s="50">
+      <c r="K19" s="49">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="L19" s="51">
+      <c r="L19" s="50">
         <f t="shared" si="0"/>
         <v>4.0266640621808545</v>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="49">
         <f t="shared" si="1"/>
         <v>142.38781416883182</v>
       </c>
-      <c r="N19" s="50">
+      <c r="N19" s="49">
         <f t="shared" si="2"/>
         <v>308.16006498154991</v>
       </c>
-      <c r="O19" s="55">
+      <c r="O19" s="54">
         <f t="shared" si="8"/>
         <v>0.46205797035172885</v>
       </c>
@@ -10235,7 +10232,7 @@
       <c r="A20" s="11">
         <v>11800</v>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="52">
         <v>12</v>
       </c>
       <c r="C20" s="11">
@@ -10250,39 +10247,39 @@
       <c r="F20" s="11">
         <v>39.1</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="49">
         <f t="shared" si="3"/>
         <v>2225</v>
       </c>
-      <c r="H20" s="50">
+      <c r="H20" s="49">
         <f t="shared" si="4"/>
         <v>1483.3333333333333</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <f t="shared" si="5"/>
         <v>5.1577152600170484E-2</v>
       </c>
-      <c r="J20" s="51">
+      <c r="J20" s="50">
         <f t="shared" si="6"/>
         <v>1.3018524000000002</v>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="49">
         <f t="shared" si="7"/>
         <v>11.8</v>
       </c>
-      <c r="L20" s="51">
+      <c r="L20" s="50">
         <f t="shared" si="0"/>
         <v>4.4139082025556826</v>
       </c>
-      <c r="M20" s="50">
+      <c r="M20" s="49">
         <f t="shared" si="1"/>
         <v>141.67374566032225</v>
       </c>
-      <c r="N20" s="50">
+      <c r="N20" s="49">
         <f t="shared" si="2"/>
         <v>303.33350357911957</v>
       </c>
-      <c r="O20" s="55">
+      <c r="O20" s="54">
         <f t="shared" si="8"/>
         <v>0.46705604223955755</v>
       </c>
@@ -10291,7 +10288,7 @@
       <c r="A21" s="11">
         <v>9500</v>
       </c>
-      <c r="B21" s="53">
+      <c r="B21" s="52">
         <v>20</v>
       </c>
       <c r="C21" s="11">
@@ -10306,39 +10303,39 @@
       <c r="F21" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="49">
         <f t="shared" si="3"/>
         <v>2232.6666666666665</v>
       </c>
-      <c r="H21" s="50">
+      <c r="H21" s="49">
         <f t="shared" si="4"/>
         <v>1488.4444444444443</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="17">
         <f t="shared" si="5"/>
         <v>5.0736961451247176E-2</v>
       </c>
-      <c r="J21" s="51">
+      <c r="J21" s="50">
         <f t="shared" si="6"/>
         <v>1.2279634800000001</v>
       </c>
-      <c r="K21" s="50">
+      <c r="K21" s="49">
         <f t="shared" si="7"/>
         <v>9.5</v>
       </c>
-      <c r="L21" s="51">
+      <c r="L21" s="50">
         <f t="shared" si="0"/>
         <v>5.1406868536623485</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="49">
         <f t="shared" si="1"/>
         <v>132.83998776852053</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="49">
         <f t="shared" si="2"/>
         <v>287.10314996803606</v>
       </c>
-      <c r="O21" s="55">
+      <c r="O21" s="54">
         <f t="shared" si="8"/>
         <v>0.46269080566796272</v>
       </c>
@@ -10347,7 +10344,7 @@
       <c r="A22" s="11">
         <v>8100</v>
       </c>
-      <c r="B22" s="53">
+      <c r="B22" s="52">
         <v>25</v>
       </c>
       <c r="C22" s="11">
@@ -10362,39 +10359,39 @@
       <c r="F22" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="49">
         <f t="shared" si="3"/>
         <v>2240.6666666666665</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="49">
         <f t="shared" si="4"/>
         <v>1493.7777777777776</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="17">
         <f t="shared" si="5"/>
         <v>4.7335600907029596E-2</v>
       </c>
-      <c r="J22" s="51">
+      <c r="J22" s="50">
         <f t="shared" si="6"/>
         <v>1.1663893800000003</v>
       </c>
-      <c r="K22" s="50">
+      <c r="K22" s="49">
         <f t="shared" si="7"/>
         <v>8.1</v>
       </c>
-      <c r="L22" s="51">
+      <c r="L22" s="50">
         <f t="shared" si="0"/>
         <v>5.5445970424230921</v>
       </c>
-      <c r="M22" s="50">
+      <c r="M22" s="49">
         <f t="shared" si="1"/>
         <v>122.16282860608972</v>
       </c>
-      <c r="N22" s="50">
+      <c r="N22" s="49">
         <f t="shared" si="2"/>
         <v>273.684012295174</v>
       </c>
-      <c r="O22" s="55">
+      <c r="O22" s="54">
         <f t="shared" si="8"/>
         <v>0.44636450474985923</v>
       </c>
@@ -10403,7 +10400,7 @@
       <c r="A23" s="11">
         <v>7200</v>
       </c>
-      <c r="B23" s="53">
+      <c r="B23" s="52">
         <v>27</v>
       </c>
       <c r="C23" s="11">
@@ -10418,39 +10415,39 @@
       <c r="F23" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="49">
         <f t="shared" si="3"/>
         <v>2244.6666666666665</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="49">
         <f t="shared" si="4"/>
         <v>1496.4444444444443</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="17">
         <f t="shared" si="5"/>
         <v>4.5634920634920695E-2</v>
       </c>
-      <c r="J23" s="51">
+      <c r="J23" s="50">
         <f t="shared" si="6"/>
         <v>1.1259264000000002</v>
       </c>
-      <c r="K23" s="50">
+      <c r="K23" s="49">
         <f t="shared" si="7"/>
         <v>7.2</v>
       </c>
-      <c r="L23" s="51">
+      <c r="L23" s="50">
         <f t="shared" si="0"/>
         <v>5.6973240263700138</v>
       </c>
-      <c r="M23" s="50">
+      <c r="M23" s="49">
         <f t="shared" si="1"/>
         <v>111.5802907020644</v>
       </c>
-      <c r="N23" s="50">
+      <c r="N23" s="49">
         <f t="shared" si="2"/>
         <v>264.66132207412619</v>
       </c>
-      <c r="O23" s="55">
+      <c r="O23" s="54">
         <f t="shared" si="8"/>
         <v>0.42159651371654927</v>
       </c>
@@ -10459,7 +10456,7 @@
       <c r="A24" s="11">
         <v>6400</v>
       </c>
-      <c r="B24" s="53">
+      <c r="B24" s="52">
         <v>30</v>
       </c>
       <c r="C24" s="11">
@@ -10474,39 +10471,39 @@
       <c r="F24" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="49">
         <f t="shared" si="3"/>
         <v>2248.6666666666665</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="49">
         <f t="shared" si="4"/>
         <v>1499.1111111111111</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="17">
         <f t="shared" si="5"/>
         <v>4.3934240362811905E-2</v>
       </c>
-      <c r="J24" s="51">
+      <c r="J24" s="50">
         <f t="shared" si="6"/>
         <v>1.0872226800000002</v>
       </c>
-      <c r="K24" s="50">
+      <c r="K24" s="49">
         <f t="shared" si="7"/>
         <v>6.4</v>
       </c>
-      <c r="L24" s="51">
+      <c r="L24" s="50">
         <f t="shared" si="0"/>
         <v>5.8463640367306828</v>
       </c>
-      <c r="M24" s="50">
+      <c r="M24" s="49">
         <f t="shared" si="1"/>
         <v>101.77705974074206</v>
       </c>
-      <c r="N24" s="50">
+      <c r="N24" s="49">
         <f t="shared" si="2"/>
         <v>256.01900389906865</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="54">
         <f t="shared" si="8"/>
         <v>0.39753712884870851</v>
       </c>
@@ -10515,7 +10512,7 @@
       <c r="A25" s="11">
         <v>5500</v>
       </c>
-      <c r="B25" s="53">
+      <c r="B25" s="52">
         <v>34</v>
       </c>
       <c r="C25" s="11">
@@ -10530,39 +10527,39 @@
       <c r="F25" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G25" s="50">
+      <c r="G25" s="49">
         <f t="shared" si="3"/>
         <v>2254.6666666666665</v>
       </c>
-      <c r="H25" s="50">
+      <c r="H25" s="49">
         <f t="shared" si="4"/>
         <v>1503.1111111111111</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="17">
         <f t="shared" si="5"/>
         <v>4.1383219954648554E-2</v>
       </c>
-      <c r="J25" s="51">
+      <c r="J25" s="50">
         <f t="shared" si="6"/>
         <v>1.0379634</v>
       </c>
-      <c r="K25" s="50">
+      <c r="K25" s="49">
         <f t="shared" si="7"/>
         <v>5.5</v>
       </c>
-      <c r="L25" s="51">
+      <c r="L25" s="50">
         <f t="shared" si="0"/>
         <v>5.9855758141703879</v>
       </c>
-      <c r="M25" s="50">
+      <c r="M25" s="49">
         <f t="shared" si="1"/>
         <v>89.547341643351913</v>
       </c>
-      <c r="N25" s="50">
+      <c r="N25" s="49">
         <f t="shared" si="2"/>
         <v>245.07160901779673</v>
       </c>
-      <c r="O25" s="55">
+      <c r="O25" s="54">
         <f t="shared" si="8"/>
         <v>0.36539255608693993</v>
       </c>
@@ -10571,7 +10568,7 @@
       <c r="A26" s="11">
         <v>4800</v>
       </c>
-      <c r="B26" s="53">
+      <c r="B26" s="52">
         <v>38</v>
       </c>
       <c r="C26" s="11">
@@ -10586,39 +10583,39 @@
       <c r="F26" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="G26" s="50">
+      <c r="G26" s="49">
         <f t="shared" si="3"/>
         <v>2261.3333333333335</v>
       </c>
-      <c r="H26" s="50">
+      <c r="H26" s="49">
         <f t="shared" si="4"/>
         <v>1507.5555555555557</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="17">
         <f t="shared" si="5"/>
         <v>3.8548752834467015E-2</v>
       </c>
-      <c r="J26" s="51">
+      <c r="J26" s="50">
         <f t="shared" si="6"/>
         <v>0.98518560000000022</v>
       </c>
-      <c r="K26" s="50">
+      <c r="K26" s="49">
         <f t="shared" si="7"/>
         <v>4.8</v>
       </c>
-      <c r="L26" s="51">
+      <c r="L26" s="50">
         <f t="shared" si="0"/>
         <v>6.0305693310778379</v>
       </c>
-      <c r="M26" s="50">
+      <c r="M26" s="49">
         <f t="shared" si="1"/>
         <v>78.737863126167227</v>
       </c>
-      <c r="N26" s="50">
+      <c r="N26" s="49">
         <f t="shared" si="2"/>
         <v>233.29813006118403</v>
       </c>
-      <c r="O26" s="55">
+      <c r="O26" s="54">
         <f t="shared" si="8"/>
         <v>0.33749890367967239</v>
       </c>
@@ -10626,18 +10623,18 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="19"/>
-      <c r="T27" s="22"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="18"/>
+      <c r="T27" s="21"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="22" t="s">
         <v>90</v>
       </c>
     </row>
@@ -10754,7 +10751,7 @@
       <c r="A32" s="11">
         <v>12400</v>
       </c>
-      <c r="B32" s="53">
+      <c r="B32" s="52">
         <v>9</v>
       </c>
       <c r="C32" s="11">
@@ -10769,39 +10766,39 @@
       <c r="F32" s="11">
         <v>31.3</v>
       </c>
-      <c r="G32" s="50">
+      <c r="G32" s="49">
         <f>D32/3</f>
         <v>1780.6666666666667</v>
       </c>
-      <c r="H32" s="50">
+      <c r="H32" s="49">
         <f>G32/1.5</f>
         <v>1187.1111111111111</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="17">
         <f>1-(G32/(60*F32))</f>
         <v>5.1828186013489486E-2</v>
       </c>
-      <c r="J32" s="51">
+      <c r="J32" s="50">
         <f t="shared" ref="J32:J41" si="9">((E32/1000)*Tyngdacc)*Hävarm</f>
         <v>0.98518560000000022</v>
       </c>
-      <c r="K32" s="50">
+      <c r="K32" s="49">
         <f>A32/1000</f>
         <v>12.4</v>
       </c>
-      <c r="L32" s="51">
+      <c r="L32" s="50">
         <f t="shared" ref="L32:L41" si="10">delta_z+((C32-ABS(B32/10))*1000/(Densitet*Tyngdacc))+(((4*(K32/3600))/(π*PumpDiam_tryck^2))^2-((4*(K32/3600))/(π*PumpDiam_sug^2))^2)/(2*Tyngdacc)</f>
         <v>1.9243124674288614</v>
       </c>
-      <c r="M32" s="50">
+      <c r="M32" s="49">
         <f t="shared" ref="M32:M41" si="11">Densitet*Tyngdacc*(K32/3600)*L32</f>
         <v>64.905477741527278</v>
       </c>
-      <c r="N32" s="50">
+      <c r="N32" s="49">
         <f t="shared" ref="N32:N41" si="12">((G32*2*π)/60)*J32</f>
         <v>183.70852163721185</v>
       </c>
-      <c r="O32" s="55">
+      <c r="O32" s="54">
         <f>M32/N32</f>
         <v>0.35330684261725659</v>
       </c>
@@ -10813,7 +10810,7 @@
       <c r="A33" s="11">
         <v>11400</v>
       </c>
-      <c r="B33" s="53">
+      <c r="B33" s="52">
         <v>13</v>
       </c>
       <c r="C33" s="11">
@@ -10828,39 +10825,39 @@
       <c r="F33" s="11">
         <v>31.3</v>
       </c>
-      <c r="G33" s="50">
+      <c r="G33" s="49">
         <f t="shared" ref="G33:G41" si="13">D33/3</f>
         <v>1782.6666666666667</v>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="49">
         <f t="shared" ref="H33:H41" si="14">G33/1.5</f>
         <v>1188.4444444444446</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="17">
         <f t="shared" ref="I33:I41" si="15">1-(G33/(60*F33))</f>
         <v>5.0763223287184855E-2</v>
       </c>
-      <c r="J33" s="51">
+      <c r="J33" s="50">
         <f t="shared" si="9"/>
         <v>0.97638930000000013</v>
       </c>
-      <c r="K33" s="50">
+      <c r="K33" s="49">
         <f t="shared" ref="K33:K41" si="16">A33/1000</f>
         <v>11.4</v>
       </c>
-      <c r="L33" s="51">
+      <c r="L33" s="50">
         <f t="shared" si="10"/>
         <v>2.2382106669079334</v>
       </c>
-      <c r="M33" s="50">
+      <c r="M33" s="49">
         <f t="shared" si="11"/>
         <v>69.404860341633466</v>
       </c>
-      <c r="N33" s="50">
+      <c r="N33" s="49">
         <f t="shared" si="12"/>
         <v>182.2727614765316</v>
       </c>
-      <c r="O33" s="55">
+      <c r="O33" s="54">
         <f t="shared" ref="O33:O41" si="17">M33/N33</f>
         <v>0.38077472343869462</v>
       </c>
@@ -10872,7 +10869,7 @@
       <c r="A34" s="11">
         <v>10500</v>
       </c>
-      <c r="B34" s="53">
+      <c r="B34" s="52">
         <v>16</v>
       </c>
       <c r="C34" s="11">
@@ -10887,39 +10884,39 @@
       <c r="F34" s="11">
         <v>31.3</v>
       </c>
-      <c r="G34" s="50">
+      <c r="G34" s="49">
         <f t="shared" si="13"/>
         <v>1784</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="49">
         <f t="shared" si="14"/>
         <v>1189.3333333333333</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="17">
         <f t="shared" si="15"/>
         <v>5.0053248136315176E-2</v>
       </c>
-      <c r="J34" s="51">
+      <c r="J34" s="50">
         <f t="shared" si="9"/>
         <v>0.95879670000000017</v>
       </c>
-      <c r="K34" s="50">
+      <c r="K34" s="49">
         <f t="shared" si="16"/>
         <v>10.5</v>
       </c>
-      <c r="L34" s="51">
+      <c r="L34" s="50">
         <f t="shared" si="10"/>
         <v>2.5715553951777754</v>
       </c>
-      <c r="M34" s="50">
+      <c r="M34" s="49">
         <f t="shared" si="11"/>
         <v>73.446187212783968</v>
       </c>
-      <c r="N34" s="50">
+      <c r="N34" s="49">
         <f t="shared" si="12"/>
         <v>179.12244085023164</v>
       </c>
-      <c r="O34" s="55">
+      <c r="O34" s="54">
         <f t="shared" si="17"/>
         <v>0.41003342107309715</v>
       </c>
@@ -10931,7 +10928,7 @@
       <c r="A35" s="11">
         <v>9600</v>
       </c>
-      <c r="B35" s="53">
+      <c r="B35" s="52">
         <v>20</v>
       </c>
       <c r="C35" s="11">
@@ -10946,39 +10943,39 @@
       <c r="F35" s="11">
         <v>31.3</v>
       </c>
-      <c r="G35" s="50">
+      <c r="G35" s="49">
         <f t="shared" si="13"/>
         <v>1791.6666666666667</v>
       </c>
-      <c r="H35" s="50">
+      <c r="H35" s="49">
         <f t="shared" si="14"/>
         <v>1194.4444444444446</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="17">
         <f t="shared" si="15"/>
         <v>4.5970891018814353E-2</v>
       </c>
-      <c r="J35" s="51">
+      <c r="J35" s="50">
         <f t="shared" si="9"/>
         <v>0.93768558000000013</v>
       </c>
-      <c r="K35" s="50">
+      <c r="K35" s="49">
         <f t="shared" si="16"/>
         <v>9.6</v>
       </c>
-      <c r="L35" s="51">
+      <c r="L35" s="50">
         <f t="shared" si="10"/>
         <v>2.8983457236278789</v>
       </c>
-      <c r="M35" s="50">
+      <c r="M35" s="49">
         <f t="shared" si="11"/>
         <v>75.684246826671128</v>
       </c>
-      <c r="N35" s="50">
+      <c r="N35" s="49">
         <f t="shared" si="12"/>
         <v>175.93128273433146</v>
       </c>
-      <c r="O35" s="55">
+      <c r="O35" s="54">
         <f t="shared" si="17"/>
         <v>0.4301920934718565</v>
       </c>
@@ -10990,7 +10987,7 @@
       <c r="A36" s="11">
         <v>8700</v>
       </c>
-      <c r="B36" s="53">
+      <c r="B36" s="52">
         <v>23</v>
       </c>
       <c r="C36" s="11">
@@ -11005,39 +11002,39 @@
       <c r="F36" s="11">
         <v>31.3</v>
       </c>
-      <c r="G36" s="50">
+      <c r="G36" s="49">
         <f t="shared" si="13"/>
         <v>1789.6666666666667</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="49">
         <f t="shared" si="14"/>
         <v>1193.1111111111111</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="17">
         <f t="shared" si="15"/>
         <v>4.7035853745118872E-2</v>
       </c>
-      <c r="J36" s="51">
+      <c r="J36" s="50">
         <f t="shared" si="9"/>
         <v>0.92361150000000014</v>
       </c>
-      <c r="K36" s="50">
+      <c r="K36" s="49">
         <f t="shared" si="16"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="L36" s="51">
+      <c r="L36" s="50">
         <f t="shared" si="10"/>
         <v>3.1368851592231763</v>
       </c>
-      <c r="M36" s="50">
+      <c r="M36" s="49">
         <f t="shared" si="11"/>
         <v>74.233843043441325</v>
       </c>
-      <c r="N36" s="50">
+      <c r="N36" s="49">
         <f t="shared" si="12"/>
         <v>173.09722236583741</v>
       </c>
-      <c r="O36" s="55">
+      <c r="O36" s="54">
         <f t="shared" si="17"/>
         <v>0.42885635037256475</v>
       </c>
@@ -11049,7 +11046,7 @@
       <c r="A37" s="11">
         <v>7900</v>
       </c>
-      <c r="B37" s="53">
+      <c r="B37" s="52">
         <v>25</v>
       </c>
       <c r="C37" s="11">
@@ -11064,39 +11061,39 @@
       <c r="F37" s="11">
         <v>31.3</v>
       </c>
-      <c r="G37" s="50">
+      <c r="G37" s="49">
         <f t="shared" si="13"/>
         <v>1791</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="49">
         <f t="shared" si="14"/>
         <v>1194</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="17">
         <f t="shared" si="15"/>
         <v>4.6325878594249192E-2</v>
       </c>
-      <c r="J37" s="51">
+      <c r="J37" s="50">
         <f t="shared" si="9"/>
         <v>0.8972226000000002</v>
       </c>
-      <c r="K37" s="50">
+      <c r="K37" s="49">
         <f t="shared" si="16"/>
         <v>7.9</v>
       </c>
-      <c r="L37" s="51">
+      <c r="L37" s="50">
         <f t="shared" si="10"/>
         <v>3.2907184729767183</v>
       </c>
-      <c r="M37" s="50">
+      <c r="M37" s="49">
         <f t="shared" si="11"/>
         <v>70.713428231537691</v>
       </c>
-      <c r="N37" s="50">
+      <c r="N37" s="49">
         <f t="shared" si="12"/>
         <v>168.27686334904561</v>
       </c>
-      <c r="O37" s="55">
+      <c r="O37" s="54">
         <f t="shared" si="17"/>
         <v>0.42022074112982177</v>
       </c>
@@ -11108,7 +11105,7 @@
       <c r="A38" s="11">
         <v>7000</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="52">
         <v>27</v>
       </c>
       <c r="C38" s="11">
@@ -11123,39 +11120,39 @@
       <c r="F38" s="11">
         <v>31.3</v>
       </c>
-      <c r="G38" s="50">
+      <c r="G38" s="49">
         <f t="shared" si="13"/>
         <v>1794.6666666666667</v>
       </c>
-      <c r="H38" s="50">
+      <c r="H38" s="49">
         <f t="shared" si="14"/>
         <v>1196.4444444444446</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="17">
         <f t="shared" si="15"/>
         <v>4.4373446929357407E-2</v>
       </c>
-      <c r="J38" s="51">
+      <c r="J38" s="50">
         <f t="shared" si="9"/>
         <v>0.87963000000000013</v>
       </c>
-      <c r="K38" s="50">
+      <c r="K38" s="49">
         <f t="shared" si="16"/>
         <v>7</v>
       </c>
-      <c r="L38" s="51">
+      <c r="L38" s="50">
         <f t="shared" si="10"/>
         <v>3.4442582706591165</v>
       </c>
-      <c r="M38" s="50">
+      <c r="M38" s="49">
         <f t="shared" si="11"/>
         <v>65.58096790509957</v>
       </c>
-      <c r="N38" s="50">
+      <c r="N38" s="49">
         <f t="shared" si="12"/>
         <v>165.31507068225326</v>
       </c>
-      <c r="O38" s="55">
+      <c r="O38" s="54">
         <f t="shared" si="17"/>
         <v>0.39670289970810113</v>
       </c>
@@ -11167,7 +11164,7 @@
       <c r="A39" s="11">
         <v>6200</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="52">
         <v>29</v>
       </c>
       <c r="C39" s="11">
@@ -11182,39 +11179,39 @@
       <c r="F39" s="11">
         <v>31.3</v>
       </c>
-      <c r="G39" s="50">
+      <c r="G39" s="49">
         <f t="shared" si="13"/>
         <v>1798</v>
       </c>
-      <c r="H39" s="50">
+      <c r="H39" s="49">
         <f t="shared" si="14"/>
         <v>1198.6666666666667</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="17">
         <f t="shared" si="15"/>
         <v>4.2598509052183209E-2</v>
       </c>
-      <c r="J39" s="51">
+      <c r="J39" s="50">
         <f t="shared" si="9"/>
         <v>0.84972258000000001</v>
       </c>
-      <c r="K39" s="50">
+      <c r="K39" s="49">
         <f t="shared" si="16"/>
         <v>6.2</v>
       </c>
-      <c r="L39" s="51">
+      <c r="L39" s="50">
         <f t="shared" si="10"/>
         <v>3.6042328437473707</v>
       </c>
-      <c r="M39" s="50">
+      <c r="M39" s="49">
         <f t="shared" si="11"/>
         <v>60.783905570100636</v>
       </c>
-      <c r="N39" s="50">
+      <c r="N39" s="49">
         <f t="shared" si="12"/>
         <v>159.99096741404745</v>
       </c>
-      <c r="O39" s="55">
+      <c r="O39" s="54">
         <f t="shared" si="17"/>
         <v>0.37992085773689571</v>
       </c>
@@ -11223,7 +11220,7 @@
       <c r="A40" s="11">
         <v>5400</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="52">
         <v>31</v>
       </c>
       <c r="C40" s="11">
@@ -11238,39 +11235,39 @@
       <c r="F40" s="11">
         <v>31.4</v>
       </c>
-      <c r="G40" s="50">
+      <c r="G40" s="49">
         <f t="shared" si="13"/>
         <v>1801.3333333333333</v>
       </c>
-      <c r="H40" s="50">
+      <c r="H40" s="49">
         <f t="shared" si="14"/>
         <v>1200.8888888888889</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="17">
         <f t="shared" si="15"/>
         <v>4.3878273177636262E-2</v>
       </c>
-      <c r="J40" s="51">
+      <c r="J40" s="50">
         <f t="shared" si="9"/>
         <v>0.81101886000000023</v>
       </c>
-      <c r="K40" s="50">
+      <c r="K40" s="49">
         <f t="shared" si="16"/>
         <v>5.4</v>
       </c>
-      <c r="L40" s="51">
+      <c r="L40" s="50">
         <f t="shared" si="10"/>
         <v>3.6649768049345961</v>
       </c>
-      <c r="M40" s="50">
+      <c r="M40" s="49">
         <f t="shared" si="11"/>
         <v>53.833059443980282</v>
       </c>
-      <c r="N40" s="50">
+      <c r="N40" s="49">
         <f t="shared" si="12"/>
         <v>152.98669314514834</v>
       </c>
-      <c r="O40" s="55">
+      <c r="O40" s="54">
         <f t="shared" si="17"/>
         <v>0.35188066580996941</v>
       </c>
@@ -11279,7 +11276,7 @@
       <c r="A41" s="11">
         <v>4400</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="52">
         <v>35</v>
       </c>
       <c r="C41" s="11">
@@ -11294,39 +11291,39 @@
       <c r="F41" s="11">
         <v>31.4</v>
       </c>
-      <c r="G41" s="50">
+      <c r="G41" s="49">
         <f t="shared" si="13"/>
         <v>1806</v>
       </c>
-      <c r="H41" s="50">
+      <c r="H41" s="49">
         <f t="shared" si="14"/>
         <v>1204</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="17">
         <f t="shared" si="15"/>
         <v>4.1401273885350309E-2</v>
       </c>
-      <c r="J41" s="51">
+      <c r="J41" s="50">
         <f t="shared" si="9"/>
         <v>0.77407440000000016</v>
       </c>
-      <c r="K41" s="50">
+      <c r="K41" s="49">
         <f t="shared" si="16"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L41" s="51">
+      <c r="L41" s="50">
         <f t="shared" si="10"/>
         <v>3.8062431948723123</v>
       </c>
-      <c r="M41" s="50">
+      <c r="M41" s="49">
         <f t="shared" si="11"/>
         <v>45.5547095658873</v>
       </c>
-      <c r="N41" s="50">
+      <c r="N41" s="49">
         <f t="shared" si="12"/>
         <v>146.39595219199003</v>
       </c>
-      <c r="O41" s="55">
+      <c r="O41" s="54">
         <f t="shared" si="17"/>
         <v>0.31117465260340577</v>
       </c>
@@ -11334,24 +11331,24 @@
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="28"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="27"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="28"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="27"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
@@ -11359,7 +11356,7 @@
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="24"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="13" t="s">
         <v>70</v>
       </c>
@@ -11390,11 +11387,11 @@
         <v>19</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="G45" s="26"/>
+      <c r="G45" s="25"/>
       <c r="K45" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="28">
         <f>π*PumphjulsDiam*(Euler_rpm/60)</f>
         <v>8.6142470561432134</v>
       </c>
@@ -11426,7 +11423,7 @@
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="26"/>
+      <c r="G47" s="25"/>
       <c r="H47" s="9" t="s">
         <v>2</v>
       </c>
@@ -11444,28 +11441,28 @@
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="50">
+      <c r="A48" s="49">
         <f t="shared" ref="A48:A57" si="18">K17*1500/H17</f>
         <v>15.815560228296786</v>
       </c>
-      <c r="B48" s="51">
+      <c r="B48" s="50">
         <f>L17*(1500/H17)^2</f>
         <v>2.752586225315953</v>
       </c>
-      <c r="C48" s="50">
+      <c r="C48" s="49">
         <f>M17*(1500/H17)^3</f>
         <v>118.41578128663245</v>
       </c>
-      <c r="D48" s="50">
+      <c r="D48" s="49">
         <f>N17*(1500/H17)^3</f>
         <v>325.5026188121559</v>
       </c>
-      <c r="E48" s="55">
+      <c r="E48" s="54">
         <f>C48/D48</f>
         <v>0.36379363618874272</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="G48" s="26"/>
+      <c r="G48" s="25"/>
       <c r="H48" s="9" t="s">
         <v>106</v>
       </c>
@@ -11483,94 +11480,94 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="50">
+      <c r="A49" s="49">
         <f t="shared" si="18"/>
         <v>14.178544636159041</v>
       </c>
-      <c r="B49" s="51">
+      <c r="B49" s="50">
         <f t="shared" ref="B49:B57" si="19">L18*(1500/H18)^2</f>
         <v>3.7107374428527651</v>
       </c>
-      <c r="C49" s="50">
+      <c r="C49" s="49">
         <f t="shared" ref="C49:C57" si="20">M18*(1500/H18)^3</f>
         <v>143.11196781039283</v>
       </c>
-      <c r="D49" s="50">
+      <c r="D49" s="49">
         <f t="shared" ref="D49:D57" si="21">N18*(1500/H18)^3</f>
         <v>324.3940953389249</v>
       </c>
-      <c r="E49" s="55">
+      <c r="E49" s="54">
         <f t="shared" ref="E49:E57" si="22">C49/D49</f>
         <v>0.44116699368670798</v>
       </c>
       <c r="F49" s="5"/>
-      <c r="G49" s="19"/>
+      <c r="G49" s="18"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="50">
+      <c r="A50" s="49">
         <f t="shared" si="18"/>
         <v>13.150007492881763</v>
       </c>
-      <c r="B50" s="51">
+      <c r="B50" s="50">
         <f t="shared" si="19"/>
         <v>4.1201278686292948</v>
       </c>
-      <c r="C50" s="50">
+      <c r="C50" s="49">
         <f t="shared" si="20"/>
         <v>147.37396464864156</v>
       </c>
-      <c r="D50" s="50">
+      <c r="D50" s="49">
         <f t="shared" si="21"/>
         <v>318.95124444332646</v>
       </c>
-      <c r="E50" s="55">
+      <c r="E50" s="54">
         <f t="shared" si="22"/>
         <v>0.46205797035172885</v>
       </c>
       <c r="F50" s="5"/>
-      <c r="G50" s="19"/>
+      <c r="G50" s="18"/>
       <c r="H50" s="11">
         <v>0</v>
       </c>
-      <c r="I50" s="51">
+      <c r="I50" s="50">
         <f t="shared" ref="I50:I57" si="23">(H50/3600)/(π*PumphjulsDiam*PumphjulsÖppning)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="51">
+      <c r="J50" s="50">
         <f t="shared" ref="J50:J57" si="24">Euler_u2-(I50/TAN(RADIANS(Skovelvinkel)))</f>
         <v>8.6142470561432134</v>
       </c>
-      <c r="K50" s="50">
+      <c r="K50" s="49">
         <f t="shared" ref="K50:K57" si="25">Euler_u2*J50</f>
         <v>74.205252344272012</v>
       </c>
-      <c r="L50" s="52">
+      <c r="L50" s="51">
         <f t="shared" ref="L50:L57" si="26">K50/Tyngdacc</f>
         <v>7.5642459066536194</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="50">
+      <c r="A51" s="49">
         <f t="shared" si="18"/>
         <v>11.932584269662922</v>
       </c>
-      <c r="B51" s="51">
+      <c r="B51" s="50">
         <f t="shared" si="19"/>
         <v>4.51365439221071</v>
       </c>
-      <c r="C51" s="50">
+      <c r="C51" s="49">
         <f t="shared" si="20"/>
         <v>146.50312366412558</v>
       </c>
-      <c r="D51" s="50">
+      <c r="D51" s="49">
         <f t="shared" si="21"/>
         <v>313.67354324683527</v>
       </c>
-      <c r="E51" s="55">
+      <c r="E51" s="54">
         <f t="shared" si="22"/>
         <v>0.4670560422395576</v>
       </c>
@@ -11578,213 +11575,213 @@
       <c r="H51" s="11">
         <v>2</v>
       </c>
-      <c r="I51" s="51">
+      <c r="I51" s="50">
         <f t="shared" si="23"/>
         <v>0.14174207136658207</v>
       </c>
-      <c r="J51" s="51">
+      <c r="J51" s="50">
         <f t="shared" si="24"/>
         <v>8.310280203170219</v>
       </c>
-      <c r="K51" s="50">
+      <c r="K51" s="49">
         <f t="shared" si="25"/>
         <v>71.586806775884284</v>
       </c>
-      <c r="L51" s="52">
+      <c r="L51" s="51">
         <f t="shared" si="26"/>
         <v>7.2973299465733215</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="50">
+      <c r="A52" s="49">
         <f t="shared" si="18"/>
         <v>9.5737533592117057</v>
       </c>
-      <c r="B52" s="51">
+      <c r="B52" s="50">
         <f t="shared" si="19"/>
         <v>5.2208162566808838</v>
       </c>
-      <c r="C52" s="50">
+      <c r="C52" s="49">
         <f t="shared" si="20"/>
         <v>135.95798388329555</v>
       </c>
-      <c r="D52" s="50">
+      <c r="D52" s="49">
         <f t="shared" si="21"/>
         <v>293.84198306473814</v>
       </c>
-      <c r="E52" s="55">
+      <c r="E52" s="54">
         <f t="shared" si="22"/>
         <v>0.46269080566796272</v>
       </c>
       <c r="F52" s="5"/>
-      <c r="G52" s="19"/>
+      <c r="G52" s="18"/>
       <c r="H52" s="11">
         <v>4</v>
       </c>
-      <c r="I52" s="51">
+      <c r="I52" s="50">
         <f t="shared" si="23"/>
         <v>0.28348414273316414</v>
       </c>
-      <c r="J52" s="51">
+      <c r="J52" s="50">
         <f t="shared" si="24"/>
         <v>8.0063133501972228</v>
       </c>
-      <c r="K52" s="50">
+      <c r="K52" s="49">
         <f t="shared" si="25"/>
         <v>68.968361207496528</v>
       </c>
-      <c r="L52" s="52">
+      <c r="L52" s="51">
         <f t="shared" si="26"/>
         <v>7.03041398649302</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="50">
+      <c r="A53" s="49">
         <f t="shared" si="18"/>
         <v>8.1337399583457319</v>
       </c>
-      <c r="B53" s="51">
+      <c r="B53" s="50">
         <f t="shared" si="19"/>
         <v>5.590884473480398</v>
       </c>
-      <c r="C53" s="50">
+      <c r="C53" s="49">
         <f t="shared" si="20"/>
         <v>123.69577731492515</v>
       </c>
-      <c r="D53" s="50">
+      <c r="D53" s="49">
         <f t="shared" si="21"/>
         <v>277.11831025686899</v>
       </c>
-      <c r="E53" s="55">
+      <c r="E53" s="54">
         <f t="shared" si="22"/>
         <v>0.44636450474985917</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="G53" s="19"/>
+      <c r="G53" s="18"/>
       <c r="H53" s="11">
         <v>6</v>
       </c>
-      <c r="I53" s="51">
+      <c r="I53" s="50">
         <f t="shared" si="23"/>
         <v>0.42522621409974626</v>
       </c>
-      <c r="J53" s="51">
+      <c r="J53" s="50">
         <f t="shared" si="24"/>
         <v>7.7023464972242284</v>
       </c>
-      <c r="K53" s="50">
+      <c r="K53" s="49">
         <f t="shared" si="25"/>
         <v>66.349915639108801</v>
       </c>
-      <c r="L53" s="52">
+      <c r="L53" s="51">
         <f t="shared" si="26"/>
         <v>6.7634980264127211</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="50">
+      <c r="A54" s="49">
         <f t="shared" si="18"/>
         <v>7.2171072171072179</v>
       </c>
-      <c r="B54" s="51">
+      <c r="B54" s="50">
         <f t="shared" si="19"/>
         <v>5.7244299008176851</v>
       </c>
-      <c r="C54" s="50">
+      <c r="C54" s="49">
         <f t="shared" si="20"/>
         <v>112.37752704807599</v>
       </c>
-      <c r="D54" s="50">
+      <c r="D54" s="49">
         <f t="shared" si="21"/>
         <v>266.55231576139278</v>
       </c>
-      <c r="E54" s="55">
+      <c r="E54" s="54">
         <f t="shared" si="22"/>
         <v>0.42159651371654921</v>
       </c>
       <c r="F54" s="5"/>
-      <c r="G54" s="19"/>
+      <c r="G54" s="18"/>
       <c r="H54" s="11">
         <v>8</v>
       </c>
-      <c r="I54" s="51">
+      <c r="I54" s="50">
         <f t="shared" si="23"/>
         <v>0.56696828546632827</v>
       </c>
-      <c r="J54" s="51">
+      <c r="J54" s="50">
         <f t="shared" si="24"/>
         <v>7.3983796442512331</v>
       </c>
-      <c r="K54" s="50">
+      <c r="K54" s="49">
         <f t="shared" si="25"/>
         <v>63.731470070721059</v>
       </c>
-      <c r="L54" s="52">
+      <c r="L54" s="51">
         <f t="shared" si="26"/>
         <v>6.4965820663324214</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="50">
+      <c r="A55" s="49">
         <f t="shared" si="18"/>
         <v>6.403794841387489</v>
       </c>
-      <c r="B55" s="51">
+      <c r="B55" s="50">
         <f t="shared" si="19"/>
         <v>5.8532992247767801</v>
       </c>
-      <c r="C55" s="50">
+      <c r="C55" s="49">
         <f t="shared" si="20"/>
         <v>101.95821139166755</v>
       </c>
-      <c r="D55" s="50">
+      <c r="D55" s="49">
         <f t="shared" si="21"/>
         <v>256.47468875912216</v>
       </c>
-      <c r="E55" s="55">
+      <c r="E55" s="54">
         <f t="shared" si="22"/>
         <v>0.39753712884870845</v>
       </c>
       <c r="F55" s="5"/>
-      <c r="G55" s="19"/>
+      <c r="G55" s="18"/>
       <c r="H55" s="11">
         <v>10</v>
       </c>
-      <c r="I55" s="51">
+      <c r="I55" s="50">
         <f t="shared" si="23"/>
         <v>0.70871035683291039</v>
       </c>
-      <c r="J55" s="51">
+      <c r="J55" s="50">
         <f t="shared" si="24"/>
         <v>7.0944127912782378</v>
       </c>
-      <c r="K55" s="50">
+      <c r="K55" s="49">
         <f t="shared" si="25"/>
         <v>61.113024502333317</v>
       </c>
-      <c r="L55" s="52">
+      <c r="L55" s="51">
         <f t="shared" si="26"/>
         <v>6.2296661062521217</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="50">
+      <c r="A56" s="49">
         <f t="shared" si="18"/>
         <v>5.4886162034299231</v>
       </c>
-      <c r="B56" s="51">
+      <c r="B56" s="50">
         <f t="shared" si="19"/>
         <v>5.9608237918248612</v>
       </c>
-      <c r="C56" s="50">
+      <c r="C56" s="49">
         <f t="shared" si="20"/>
         <v>88.99246149894816</v>
       </c>
-      <c r="D56" s="50">
+      <c r="D56" s="49">
         <f t="shared" si="21"/>
         <v>243.55302267781741</v>
       </c>
-      <c r="E56" s="55">
+      <c r="E56" s="54">
         <f t="shared" si="22"/>
         <v>0.36539255608693999</v>
       </c>
@@ -11792,72 +11789,72 @@
       <c r="H56" s="11">
         <v>12</v>
       </c>
-      <c r="I56" s="51">
+      <c r="I56" s="50">
         <f t="shared" si="23"/>
         <v>0.85045242819949252</v>
       </c>
-      <c r="J56" s="51">
+      <c r="J56" s="50">
         <f t="shared" si="24"/>
         <v>6.7904459383052433</v>
       </c>
-      <c r="K56" s="50">
+      <c r="K56" s="49">
         <f t="shared" si="25"/>
         <v>58.494578933945583</v>
       </c>
-      <c r="L56" s="52">
+      <c r="L56" s="51">
         <f t="shared" si="26"/>
         <v>5.9627501461718229</v>
       </c>
-      <c r="M56" s="19"/>
+      <c r="M56" s="18"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="50">
+      <c r="A57" s="49">
         <f t="shared" si="18"/>
         <v>4.7759433962264151</v>
       </c>
-      <c r="B57" s="51">
+      <c r="B57" s="50">
         <f t="shared" si="19"/>
         <v>5.9702728835822505</v>
       </c>
-      <c r="C57" s="50">
+      <c r="C57" s="49">
         <f t="shared" si="20"/>
         <v>77.559932957587307</v>
       </c>
-      <c r="D57" s="50">
+      <c r="D57" s="49">
         <f t="shared" si="21"/>
         <v>229.80795526139289</v>
       </c>
-      <c r="E57" s="55">
+      <c r="E57" s="54">
         <f t="shared" si="22"/>
         <v>0.33749890367967239</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="G57" s="19"/>
+      <c r="G57" s="18"/>
       <c r="H57" s="11">
         <v>14</v>
       </c>
-      <c r="I57" s="51">
+      <c r="I57" s="50">
         <f t="shared" si="23"/>
         <v>0.99219449956607453</v>
       </c>
-      <c r="J57" s="51">
+      <c r="J57" s="50">
         <f t="shared" si="24"/>
         <v>6.4864790853322489</v>
       </c>
-      <c r="K57" s="50">
+      <c r="K57" s="49">
         <f t="shared" si="25"/>
         <v>55.876133365557848</v>
       </c>
-      <c r="L57" s="52">
+      <c r="L57" s="51">
         <f t="shared" si="26"/>
         <v>5.6958341860915231</v>
       </c>
-      <c r="M57" s="19"/>
+      <c r="M57" s="18"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="19"/>
+      <c r="G58" s="18"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
@@ -11865,11 +11862,11 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="24"/>
+      <c r="G59" s="23"/>
       <c r="H59" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="I59" s="22"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
@@ -11923,7 +11920,7 @@
         <v>37</v>
       </c>
       <c r="F61" s="5"/>
-      <c r="G61" s="24"/>
+      <c r="G61" s="23"/>
       <c r="H61" s="9" t="s">
         <v>106</v>
       </c>
@@ -11948,7 +11945,7 @@
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="F62" s="5"/>
-      <c r="G62" s="24"/>
+      <c r="G62" s="23"/>
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
@@ -11958,478 +11955,478 @@
       <c r="N62" s="9"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="50">
+      <c r="A63" s="49">
         <f>K32*1200/H32</f>
         <v>12.534631224260577</v>
       </c>
-      <c r="B63" s="51">
+      <c r="B63" s="50">
         <f>L32*(1200/H32)^2</f>
         <v>1.9663252036981085</v>
       </c>
-      <c r="C63" s="50">
+      <c r="C63" s="49">
         <f>M32*(1200/H32)^3</f>
         <v>67.04262020360666</v>
       </c>
-      <c r="D63" s="50">
+      <c r="D63" s="49">
         <f>N32*(1200/H32)^3</f>
         <v>189.75749155312877</v>
       </c>
-      <c r="E63" s="55">
+      <c r="E63" s="54">
         <f>C63/D63</f>
         <v>0.35330684261725659</v>
       </c>
       <c r="F63" s="5"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="50">
+      <c r="G63" s="23"/>
+      <c r="H63" s="49">
         <f>K32*1500/H32</f>
         <v>15.66828903032572</v>
       </c>
-      <c r="I63" s="51">
+      <c r="I63" s="50">
         <f>L32*(1500/H32)^2</f>
         <v>3.0723831307782952</v>
       </c>
-      <c r="J63" s="50">
+      <c r="J63" s="49">
         <f>M32*(1500/H32)^3</f>
         <v>130.9426175851693</v>
       </c>
-      <c r="K63" s="50">
+      <c r="K63" s="49">
         <f>N32*(1500/H32)^3</f>
         <v>370.62010068970471</v>
       </c>
-      <c r="L63" s="55">
+      <c r="L63" s="54">
         <f>J63/K63</f>
         <v>0.35330684261725659</v>
       </c>
-      <c r="M63" s="30"/>
-      <c r="N63" s="30"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="50">
+      <c r="A64" s="49">
         <f t="shared" ref="A64:A72" si="27">K33*1200/H33</f>
         <v>11.51084517576664</v>
       </c>
-      <c r="B64" s="51">
+      <c r="B64" s="50">
         <f t="shared" ref="B64:B72" si="28">L33*(1200/H33)^2</f>
         <v>2.2819476845032032</v>
       </c>
-      <c r="C64" s="50">
+      <c r="C64" s="49">
         <f t="shared" ref="C64:C72" si="29">M33*(1200/H33)^3</f>
         <v>71.449133846719377</v>
       </c>
-      <c r="D64" s="50">
+      <c r="D64" s="49">
         <f t="shared" ref="D64:D72" si="30">N33*(1200/H33)^3</f>
         <v>187.64148313595405</v>
       </c>
-      <c r="E64" s="55">
+      <c r="E64" s="54">
         <f t="shared" ref="E64:E72" si="31">C64/D64</f>
         <v>0.38077472343869456</v>
       </c>
       <c r="F64" s="5"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="50">
+      <c r="G64" s="23"/>
+      <c r="H64" s="49">
         <f t="shared" ref="H64:H72" si="32">K33*1500/H33</f>
         <v>14.3885564697083</v>
       </c>
-      <c r="I64" s="51">
+      <c r="I64" s="50">
         <f t="shared" ref="I64:I72" si="33">L33*(1500/H33)^2</f>
         <v>3.5655432570362557</v>
       </c>
-      <c r="J64" s="50">
+      <c r="J64" s="49">
         <f t="shared" ref="J64:J72" si="34">M33*(1500/H33)^3</f>
         <v>139.5490895443738</v>
       </c>
-      <c r="K64" s="50">
+      <c r="K64" s="49">
         <f t="shared" ref="K64:K72" si="35">N33*(1500/H33)^3</f>
         <v>366.48727174991035</v>
       </c>
-      <c r="L64" s="55">
+      <c r="L64" s="54">
         <f t="shared" ref="L64:L72" si="36">J64/K64</f>
         <v>0.38077472343869451</v>
       </c>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="50">
+      <c r="A65" s="49">
         <f t="shared" si="27"/>
         <v>10.594170403587444</v>
       </c>
-      <c r="B65" s="51">
+      <c r="B65" s="50">
         <f t="shared" si="28"/>
         <v>2.6178887948857783</v>
       </c>
-      <c r="C65" s="50">
+      <c r="C65" s="49">
         <f t="shared" si="29"/>
         <v>75.440093938800089</v>
       </c>
-      <c r="D65" s="50">
+      <c r="D65" s="49">
         <f t="shared" si="30"/>
         <v>183.98523159738065</v>
       </c>
-      <c r="E65" s="55">
+      <c r="E65" s="54">
         <f t="shared" si="31"/>
         <v>0.4100334210730972</v>
       </c>
       <c r="F65" s="5"/>
-      <c r="H65" s="50">
+      <c r="H65" s="49">
         <f t="shared" si="32"/>
         <v>13.242713004484306</v>
       </c>
-      <c r="I65" s="51">
+      <c r="I65" s="50">
         <f t="shared" si="33"/>
         <v>4.0904512420090295</v>
       </c>
-      <c r="J65" s="50">
+      <c r="J65" s="49">
         <f t="shared" si="34"/>
         <v>147.34393347421894</v>
       </c>
-      <c r="K65" s="50">
+      <c r="K65" s="49">
         <f t="shared" si="35"/>
         <v>359.3461554636342</v>
       </c>
-      <c r="L65" s="55">
+      <c r="L65" s="54">
         <f t="shared" si="36"/>
         <v>0.41003342107309709</v>
       </c>
-      <c r="M65" s="30"/>
-      <c r="N65" s="30"/>
+      <c r="M65" s="29"/>
+      <c r="N65" s="29"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="50">
+      <c r="A66" s="49">
         <f t="shared" si="27"/>
         <v>9.6446511627906961</v>
       </c>
-      <c r="B66" s="51">
+      <c r="B66" s="50">
         <f t="shared" si="28"/>
         <v>2.9253697800234133</v>
       </c>
-      <c r="C66" s="50">
+      <c r="C66" s="49">
         <f t="shared" si="29"/>
         <v>76.745225603597774</v>
       </c>
-      <c r="D66" s="50">
+      <c r="D66" s="49">
         <f t="shared" si="30"/>
         <v>178.39757347520501</v>
       </c>
-      <c r="E66" s="55">
+      <c r="E66" s="54">
         <f t="shared" si="31"/>
         <v>0.43019209347185644</v>
       </c>
       <c r="F66" s="5"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="50">
+      <c r="G66" s="23"/>
+      <c r="H66" s="49">
         <f t="shared" si="32"/>
         <v>12.055813953488371</v>
       </c>
-      <c r="I66" s="51">
+      <c r="I66" s="50">
         <f t="shared" si="33"/>
         <v>4.5708902812865828</v>
       </c>
-      <c r="J66" s="50">
+      <c r="J66" s="49">
         <f t="shared" si="34"/>
         <v>149.89301875702688</v>
       </c>
-      <c r="K66" s="50">
+      <c r="K66" s="49">
         <f t="shared" si="35"/>
         <v>348.43276069375975</v>
       </c>
-      <c r="L66" s="55">
+      <c r="L66" s="54">
         <f t="shared" si="36"/>
         <v>0.43019209347185644</v>
       </c>
-      <c r="M66" s="30"/>
-      <c r="N66" s="30"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="29"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="50">
+      <c r="A67" s="49">
         <f t="shared" si="27"/>
         <v>8.7502328180294278</v>
       </c>
-      <c r="B67" s="51">
+      <c r="B67" s="50">
         <f t="shared" si="28"/>
         <v>3.173213777684369</v>
       </c>
-      <c r="C67" s="50">
+      <c r="C67" s="49">
         <f t="shared" si="29"/>
         <v>75.527135198374907</v>
       </c>
-      <c r="D67" s="50">
+      <c r="D67" s="49">
         <f t="shared" si="30"/>
         <v>176.11289918584961</v>
       </c>
-      <c r="E67" s="55">
+      <c r="E67" s="54">
         <f t="shared" si="31"/>
         <v>0.42885635037256481</v>
       </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="50">
+      <c r="G67" s="23"/>
+      <c r="H67" s="49">
         <f t="shared" si="32"/>
         <v>10.937791022536784</v>
       </c>
-      <c r="I67" s="51">
+      <c r="I67" s="50">
         <f t="shared" si="33"/>
         <v>4.9581465276318264</v>
       </c>
-      <c r="J67" s="50">
+      <c r="J67" s="49">
         <f t="shared" si="34"/>
         <v>147.51393593432596</v>
       </c>
-      <c r="K67" s="50">
+      <c r="K67" s="49">
         <f t="shared" si="35"/>
         <v>343.97050622236247</v>
       </c>
-      <c r="L67" s="55">
+      <c r="L67" s="54">
         <f t="shared" si="36"/>
         <v>0.42885635037256481</v>
       </c>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="50">
+      <c r="A68" s="49">
         <f t="shared" si="27"/>
         <v>7.9396984924623117</v>
       </c>
-      <c r="B68" s="51">
+      <c r="B68" s="50">
         <f t="shared" si="28"/>
         <v>3.3238741172967523</v>
       </c>
-      <c r="C68" s="50">
+      <c r="C68" s="49">
         <f t="shared" si="29"/>
         <v>71.784825728640854</v>
       </c>
-      <c r="D68" s="50">
+      <c r="D68" s="49">
         <f t="shared" si="30"/>
         <v>170.82646976357563</v>
       </c>
-      <c r="E68" s="55">
+      <c r="E68" s="54">
         <f t="shared" si="31"/>
         <v>0.42022074112982183</v>
       </c>
       <c r="F68" s="5"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="50">
+      <c r="G68" s="23"/>
+      <c r="H68" s="49">
         <f t="shared" si="32"/>
         <v>9.924623115577889</v>
       </c>
-      <c r="I68" s="51">
+      <c r="I68" s="50">
         <f t="shared" si="33"/>
         <v>5.1935533082761784</v>
       </c>
-      <c r="J68" s="50">
+      <c r="J68" s="49">
         <f t="shared" si="34"/>
         <v>140.20473775125174</v>
       </c>
-      <c r="K68" s="50">
+      <c r="K68" s="49">
         <f t="shared" si="35"/>
         <v>333.64544875698391</v>
       </c>
-      <c r="L68" s="55">
+      <c r="L68" s="54">
         <f t="shared" si="36"/>
         <v>0.42022074112982172</v>
       </c>
-      <c r="M68" s="30"/>
-      <c r="N68" s="30"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="50">
+      <c r="A69" s="49">
         <f t="shared" si="27"/>
         <v>7.0208023774145607</v>
       </c>
-      <c r="B69" s="51">
+      <c r="B69" s="50">
         <f t="shared" si="28"/>
         <v>3.4647597627201172</v>
       </c>
-      <c r="C69" s="50">
+      <c r="C69" s="49">
         <f t="shared" si="29"/>
         <v>66.167381448019967</v>
       </c>
-      <c r="D69" s="50">
+      <c r="D69" s="49">
         <f t="shared" si="30"/>
         <v>166.79328912570776</v>
       </c>
-      <c r="E69" s="55">
+      <c r="E69" s="54">
         <f t="shared" si="31"/>
         <v>0.39670289970810119</v>
       </c>
       <c r="F69" s="5"/>
-      <c r="H69" s="50">
+      <c r="H69" s="49">
         <f t="shared" si="32"/>
         <v>8.776002971768202</v>
       </c>
-      <c r="I69" s="51">
+      <c r="I69" s="50">
         <f t="shared" si="33"/>
         <v>5.4136871292501807</v>
       </c>
-      <c r="J69" s="50">
+      <c r="J69" s="49">
         <f t="shared" si="34"/>
         <v>129.23316689066394</v>
       </c>
-      <c r="K69" s="50">
+      <c r="K69" s="49">
         <f t="shared" si="35"/>
         <v>325.76814282364779</v>
       </c>
-      <c r="L69" s="55">
+      <c r="L69" s="54">
         <f t="shared" si="36"/>
         <v>0.39670289970810119</v>
       </c>
-      <c r="M69" s="30"/>
-      <c r="N69" s="30"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="50">
+      <c r="A70" s="49">
         <f t="shared" si="27"/>
         <v>6.2068965517241379</v>
       </c>
-      <c r="B70" s="51">
+      <c r="B70" s="50">
         <f t="shared" si="28"/>
         <v>3.6122556188811572</v>
       </c>
-      <c r="C70" s="50">
+      <c r="C70" s="49">
         <f t="shared" si="29"/>
         <v>60.986969675010265</v>
       </c>
-      <c r="D70" s="50">
+      <c r="D70" s="49">
         <f t="shared" si="30"/>
         <v>160.525457955365</v>
       </c>
-      <c r="E70" s="55">
+      <c r="E70" s="54">
         <f t="shared" si="31"/>
         <v>0.37992085773689577</v>
       </c>
       <c r="F70" s="5"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="50">
+      <c r="G70" s="23"/>
+      <c r="H70" s="49">
         <f t="shared" si="32"/>
         <v>7.7586206896551717</v>
       </c>
-      <c r="I70" s="51">
+      <c r="I70" s="50">
         <f t="shared" si="33"/>
         <v>5.6441494045018077</v>
       </c>
-      <c r="J70" s="50">
+      <c r="J70" s="49">
         <f t="shared" si="34"/>
         <v>119.11517514650441</v>
       </c>
-      <c r="K70" s="50">
+      <c r="K70" s="49">
         <f t="shared" si="35"/>
         <v>313.52628506907223</v>
       </c>
-      <c r="L70" s="55">
+      <c r="L70" s="54">
         <f t="shared" si="36"/>
         <v>0.37992085773689577</v>
       </c>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="50">
+      <c r="A71" s="49">
         <f t="shared" si="27"/>
         <v>5.3960029607697999</v>
       </c>
-      <c r="B71" s="51">
+      <c r="B71" s="50">
         <f t="shared" si="28"/>
         <v>3.6595532365987649</v>
       </c>
-      <c r="C71" s="50">
+      <c r="C71" s="49">
         <f t="shared" si="29"/>
         <v>53.713607432615539</v>
       </c>
-      <c r="D71" s="50">
+      <c r="D71" s="49">
         <f t="shared" si="30"/>
         <v>152.64722575471987</v>
       </c>
-      <c r="E71" s="55">
+      <c r="E71" s="54">
         <f t="shared" si="31"/>
         <v>0.35188066580996941</v>
       </c>
       <c r="F71" s="5"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="50">
+      <c r="G71" s="23"/>
+      <c r="H71" s="49">
         <f t="shared" si="32"/>
         <v>6.7450037009622505</v>
       </c>
-      <c r="I71" s="51">
+      <c r="I71" s="50">
         <f t="shared" si="33"/>
         <v>5.7180519321855678</v>
       </c>
-      <c r="J71" s="50">
+      <c r="J71" s="49">
         <f t="shared" si="34"/>
         <v>104.90938951682719</v>
       </c>
-      <c r="K71" s="50">
+      <c r="K71" s="49">
         <f t="shared" si="35"/>
         <v>298.13911280218713</v>
       </c>
-      <c r="L71" s="55">
+      <c r="L71" s="54">
         <f t="shared" si="36"/>
         <v>0.35188066580996946</v>
       </c>
-      <c r="M71" s="30"/>
-      <c r="N71" s="30"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="50">
+      <c r="A72" s="49">
         <f t="shared" si="27"/>
         <v>4.3853820598006648</v>
       </c>
-      <c r="B72" s="51">
+      <c r="B72" s="50">
         <f t="shared" si="28"/>
         <v>3.7809945534652827</v>
       </c>
-      <c r="C72" s="50">
+      <c r="C72" s="49">
         <f t="shared" si="29"/>
         <v>45.102182662720132</v>
       </c>
-      <c r="D72" s="50">
+      <c r="D72" s="49">
         <f t="shared" si="30"/>
         <v>144.94169844933728</v>
       </c>
-      <c r="E72" s="55">
+      <c r="E72" s="54">
         <f t="shared" si="31"/>
         <v>0.31117465260340582</v>
       </c>
       <c r="F72" s="5"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="50">
+      <c r="G72" s="23"/>
+      <c r="H72" s="49">
         <f t="shared" si="32"/>
         <v>5.4817275747508312</v>
       </c>
-      <c r="I72" s="51">
+      <c r="I72" s="50">
         <f t="shared" si="33"/>
         <v>5.9078039897895049</v>
       </c>
-      <c r="J72" s="50">
+      <c r="J72" s="49">
         <f t="shared" si="34"/>
         <v>88.090200513125268</v>
       </c>
-      <c r="K72" s="50">
+      <c r="K72" s="49">
         <f t="shared" si="35"/>
         <v>283.08925478386192</v>
       </c>
-      <c r="L72" s="55">
+      <c r="L72" s="54">
         <f t="shared" si="36"/>
         <v>0.31117465260340582</v>
       </c>
-      <c r="M72" s="30"/>
-      <c r="N72" s="30"/>
-      <c r="O72" s="31"/>
+      <c r="M72" s="29"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="26"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
       <c r="O73" s="5"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
       <c r="O74" s="5"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
@@ -12445,7 +12442,7 @@
       <c r="A77" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="31">
         <v>0.06</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -12454,7 +12451,7 @@
       <c r="D77" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E77" s="32">
+      <c r="E77" s="31">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -12463,7 +12460,7 @@
       <c r="G77" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H77" s="32">
+      <c r="H77" s="31">
         <v>2</v>
       </c>
       <c r="I77" s="3" t="s">
@@ -12475,7 +12472,7 @@
       <c r="A78" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="31">
         <v>0.05</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -12484,7 +12481,7 @@
       <c r="D78" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E78" s="32">
+      <c r="E78" s="31">
         <v>20</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -12493,11 +12490,11 @@
       <c r="G78" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H78" s="61">
+      <c r="H78" s="60">
         <f>0.5+(2*0.3)+(2*1.1)</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="I78" s="33" t="s">
+      <c r="I78" s="32" t="s">
         <v>30</v>
       </c>
       <c r="O78" s="5"/>
@@ -12506,7 +12503,7 @@
       <c r="A79" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="31">
         <v>1E-4</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -12515,10 +12512,10 @@
       <c r="D79" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E79" s="32">
+      <c r="E79" s="31">
         <v>1.005E-3</v>
       </c>
-      <c r="F79" s="34" t="s">
+      <c r="F79" s="33" t="s">
         <v>41</v>
       </c>
       <c r="G79" s="5" t="s">
@@ -12528,7 +12525,7 @@
         <f>0.5+2+(3*0.3)+1.1+1.05</f>
         <v>5.55</v>
       </c>
-      <c r="I79" s="35" t="s">
+      <c r="I79" s="34" t="s">
         <v>30</v>
       </c>
       <c r="O79" s="5"/>
@@ -12617,588 +12614,588 @@
       <c r="A84" s="11">
         <v>0.01</v>
       </c>
-      <c r="B84" s="36">
+      <c r="B84" s="35">
         <f t="shared" ref="B84:B98" si="37">(Densitet*((A84/3600)/(((RörDiam_sug/2)^2)*π))*RörDiam_sug)/Dynamisk_viskositet</f>
         <v>58.547434750075531</v>
       </c>
-      <c r="C84" s="36">
+      <c r="C84" s="35">
         <f t="shared" ref="C84:C98" si="38">(Densitet*((A84/3600)/(((RörDiam_tryck/2)^2)*π))*RörDiam_tryck)/Dynamisk_viskositet</f>
         <v>70.256921700090629</v>
       </c>
-      <c r="D84" s="56">
+      <c r="D84" s="55">
         <f t="shared" ref="D84:D98" si="39">8*((8/B84)^12+((-2.457*LN((7/B84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/B84)^16)^-1.5)^(1/12)</f>
         <v>1.0931307284973306</v>
       </c>
-      <c r="E84" s="56">
+      <c r="E84" s="55">
         <f t="shared" ref="E84:E98" si="40">8*((8/C84)^12+((-2.457*LN((7/C84)^0.9+0.27*(Ytråhet/RörDiam_sug)))^16+(37530/C84)^16)^-1.5)^(1/12)</f>
         <v>0.9109422737477757</v>
       </c>
-      <c r="F84" s="59">
+      <c r="F84" s="58">
         <f t="shared" ref="F84:F98" si="41">D84*(RörLängd_sug/RörDiam_sug)*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>4.481280076578404E-6</v>
       </c>
-      <c r="G84" s="58">
+      <c r="G84" s="57">
         <f t="shared" ref="G84:G98" si="42">E84*(RörLängd_tryck/RörDiam_tryck)*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>3.7169529467171911E-5</v>
       </c>
-      <c r="H84" s="58">
+      <c r="H84" s="57">
         <f t="shared" ref="H84:H98" si="43">H_stat+F84+G84+Engångs_sug*(((A84/3600)/(((RörDiam_sug/2)^2)*π))^2)/(2*Tyngdacc)+Engångs_tryck*(((A84/3600)/(((RörDiam_tryck/2)^2)*π))^2)/(2*Tyngdacc)</f>
         <v>2.0000423792963899</v>
       </c>
-      <c r="I84" s="59">
+      <c r="I84" s="58">
         <f t="shared" ref="I84:I98" si="44">(Hpv/Qpv^2)*A84^2</f>
         <v>3.8580104312922285E-6</v>
       </c>
-      <c r="K84" s="37"/>
+      <c r="K84" s="36"/>
       <c r="O84" s="5"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
         <v>1</v>
       </c>
-      <c r="B85" s="36">
+      <c r="B85" s="35">
         <f t="shared" si="37"/>
         <v>5854.7434750075527</v>
       </c>
-      <c r="C85" s="36">
+      <c r="C85" s="35">
         <f t="shared" si="38"/>
         <v>7025.6921700090634</v>
       </c>
-      <c r="D85" s="56">
+      <c r="D85" s="55">
         <f t="shared" si="39"/>
         <v>3.8321925128009915E-2</v>
       </c>
-      <c r="E85" s="56">
+      <c r="E85" s="55">
         <f t="shared" si="40"/>
         <v>3.6611859393007894E-2</v>
       </c>
-      <c r="F85" s="57">
+      <c r="F85" s="56">
         <f t="shared" si="41"/>
         <v>1.5710040445789141E-3</v>
       </c>
-      <c r="G85" s="56">
+      <c r="G85" s="55">
         <f t="shared" si="42"/>
         <v>1.4938878409469404E-2</v>
       </c>
-      <c r="H85" s="51">
+      <c r="H85" s="50">
         <f t="shared" si="43"/>
         <v>2.0237947509139773</v>
       </c>
-      <c r="I85" s="56">
+      <c r="I85" s="55">
         <f t="shared" si="44"/>
         <v>3.8580104312922282E-2</v>
       </c>
-      <c r="K85" s="37"/>
+      <c r="K85" s="36"/>
       <c r="O85" s="5"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>2</v>
       </c>
-      <c r="B86" s="36">
+      <c r="B86" s="35">
         <f t="shared" si="37"/>
         <v>11709.486950015105</v>
       </c>
-      <c r="C86" s="36">
+      <c r="C86" s="35">
         <f t="shared" si="38"/>
         <v>14051.384340018127</v>
       </c>
-      <c r="D86" s="56">
+      <c r="D86" s="55">
         <f t="shared" si="39"/>
         <v>3.2620438582158094E-2</v>
       </c>
-      <c r="E86" s="56">
+      <c r="E86" s="55">
         <f t="shared" si="40"/>
         <v>3.1444182088847902E-2</v>
       </c>
-      <c r="F86" s="57">
+      <c r="F86" s="56">
         <f t="shared" si="41"/>
         <v>5.3490883641491745E-3</v>
       </c>
-      <c r="G86" s="56">
+      <c r="G86" s="55">
         <f t="shared" si="42"/>
         <v>5.132116431106204E-2</v>
       </c>
-      <c r="H86" s="51">
+      <c r="H86" s="50">
         <f t="shared" si="43"/>
         <v>2.0858097265149258</v>
       </c>
-      <c r="I86" s="51">
+      <c r="I86" s="50">
         <f t="shared" si="44"/>
         <v>0.15432041725168913</v>
       </c>
-      <c r="K86" s="37"/>
+      <c r="K86" s="36"/>
       <c r="O86" s="5"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="11">
         <v>3</v>
       </c>
-      <c r="B87" s="36">
+      <c r="B87" s="35">
         <f t="shared" si="37"/>
         <v>17564.230425022655</v>
       </c>
-      <c r="C87" s="36">
+      <c r="C87" s="35">
         <f t="shared" si="38"/>
         <v>21077.076510027189</v>
       </c>
-      <c r="D87" s="56">
+      <c r="D87" s="55">
         <f t="shared" si="39"/>
         <v>3.0158934944615735E-2</v>
       </c>
-      <c r="E87" s="56">
+      <c r="E87" s="55">
         <f t="shared" si="40"/>
         <v>2.9224396022782723E-2</v>
       </c>
-      <c r="F87" s="56">
+      <c r="F87" s="55">
         <f t="shared" si="41"/>
         <v>1.1127266638595338E-2</v>
       </c>
-      <c r="G87" s="56">
+      <c r="G87" s="55">
         <f t="shared" si="42"/>
         <v>0.10732088875336367</v>
       </c>
-      <c r="H87" s="51">
+      <c r="H87" s="50">
         <f t="shared" si="43"/>
         <v>2.1840119715313184</v>
       </c>
-      <c r="I87" s="51">
+      <c r="I87" s="50">
         <f t="shared" si="44"/>
         <v>0.34722093881630056</v>
       </c>
-      <c r="K87" s="37"/>
+      <c r="K87" s="36"/>
       <c r="O87" s="5"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="11">
         <v>4</v>
       </c>
-      <c r="B88" s="36">
+      <c r="B88" s="35">
         <f t="shared" si="37"/>
         <v>23418.973900030211</v>
       </c>
-      <c r="C88" s="36">
+      <c r="C88" s="35">
         <f t="shared" si="38"/>
         <v>28102.768680036253</v>
       </c>
-      <c r="D88" s="56">
+      <c r="D88" s="55">
         <f t="shared" si="39"/>
         <v>2.8728264924052185E-2</v>
       </c>
-      <c r="E88" s="56">
+      <c r="E88" s="55">
         <f t="shared" si="40"/>
         <v>2.794059197957208E-2</v>
       </c>
-      <c r="F88" s="56">
+      <c r="F88" s="55">
         <f t="shared" si="41"/>
         <v>1.8843404234484204E-2</v>
       </c>
-      <c r="G88" s="56">
+      <c r="G88" s="55">
         <f t="shared" si="42"/>
         <v>0.18241132275347408</v>
       </c>
-      <c r="H88" s="51">
+      <c r="H88" s="50">
         <f t="shared" si="43"/>
         <v>2.317812622346819</v>
       </c>
-      <c r="I88" s="51">
+      <c r="I88" s="50">
         <f t="shared" si="44"/>
         <v>0.61728166900675652</v>
       </c>
-      <c r="K88" s="37"/>
+      <c r="K88" s="36"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="11">
         <v>5</v>
       </c>
-      <c r="B89" s="36">
+      <c r="B89" s="35">
         <f t="shared" si="37"/>
         <v>29273.717375037762</v>
       </c>
-      <c r="C89" s="36">
+      <c r="C89" s="35">
         <f t="shared" si="38"/>
         <v>35128.460850045311</v>
       </c>
-      <c r="D89" s="56">
+      <c r="D89" s="55">
         <f t="shared" si="39"/>
         <v>2.7775940661754841E-2</v>
       </c>
-      <c r="E89" s="56">
+      <c r="E89" s="55">
         <f t="shared" si="40"/>
         <v>2.7089706830084295E-2</v>
       </c>
-      <c r="F89" s="56">
+      <c r="F89" s="55">
         <f t="shared" si="41"/>
         <v>2.8466807823354017E-2</v>
       </c>
-      <c r="G89" s="56">
+      <c r="G89" s="55">
         <f t="shared" si="42"/>
         <v>0.27633794294540087</v>
       </c>
-      <c r="H89" s="51">
+      <c r="H89" s="50">
         <f t="shared" si="43"/>
         <v>2.4869264622669736</v>
       </c>
-      <c r="I89" s="51">
+      <c r="I89" s="50">
         <f t="shared" si="44"/>
         <v>0.96450260782305708</v>
       </c>
-      <c r="K89" s="37"/>
+      <c r="K89" s="36"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="11">
         <v>6</v>
       </c>
-      <c r="B90" s="36">
+      <c r="B90" s="35">
         <f t="shared" si="37"/>
         <v>35128.460850045311</v>
       </c>
-      <c r="C90" s="36">
+      <c r="C90" s="35">
         <f t="shared" si="38"/>
         <v>42154.153020054378</v>
       </c>
-      <c r="D90" s="56">
+      <c r="D90" s="55">
         <f t="shared" si="39"/>
         <v>2.7089706830084295E-2</v>
       </c>
-      <c r="E90" s="56">
+      <c r="E90" s="55">
         <f t="shared" si="40"/>
         <v>2.6478837337398559E-2</v>
       </c>
-      <c r="F90" s="56">
+      <c r="F90" s="55">
         <f t="shared" si="41"/>
         <v>3.9979447764091576E-2</v>
       </c>
-      <c r="G90" s="56">
+      <c r="G90" s="55">
         <f t="shared" si="42"/>
         <v>0.3889534420475288</v>
       </c>
-      <c r="H90" s="51">
+      <c r="H90" s="50">
         <f t="shared" si="43"/>
         <v>2.6911881543690566</v>
       </c>
-      <c r="I90" s="51">
+      <c r="I90" s="50">
         <f t="shared" si="44"/>
         <v>1.3888837552652022</v>
       </c>
-      <c r="K90" s="37"/>
+      <c r="K90" s="36"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="11">
         <v>7</v>
       </c>
-      <c r="B91" s="36">
+      <c r="B91" s="35">
         <f t="shared" si="37"/>
         <v>40983.204325052866</v>
       </c>
-      <c r="C91" s="36">
+      <c r="C91" s="35">
         <f t="shared" si="38"/>
         <v>49179.845190063432</v>
       </c>
-      <c r="D91" s="56">
+      <c r="D91" s="55">
         <f t="shared" si="39"/>
         <v>2.6568562047799192E-2</v>
       </c>
-      <c r="E91" s="56">
+      <c r="E91" s="55">
         <f t="shared" si="40"/>
         <v>2.6016407424642111E-2</v>
       </c>
-      <c r="F91" s="56">
+      <c r="F91" s="55">
         <f t="shared" si="41"/>
         <v>5.3369620563667931E-2</v>
       </c>
-      <c r="G91" s="56">
+      <c r="G91" s="55">
         <f t="shared" si="42"/>
         <v>0.52016318556239094</v>
       </c>
-      <c r="H91" s="51">
+      <c r="H91" s="50">
         <f t="shared" si="43"/>
         <v>2.9304913606625691</v>
       </c>
-      <c r="I91" s="51">
+      <c r="I91" s="50">
         <f t="shared" si="44"/>
         <v>1.8904251113331918</v>
       </c>
-      <c r="K91" s="37"/>
+      <c r="K91" s="36"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="11">
         <v>8</v>
       </c>
-      <c r="B92" s="36">
+      <c r="B92" s="35">
         <f t="shared" si="37"/>
         <v>46837.947800060421</v>
       </c>
-      <c r="C92" s="36">
+      <c r="C92" s="35">
         <f t="shared" si="38"/>
         <v>56205.537360072507</v>
       </c>
-      <c r="D92" s="56">
+      <c r="D92" s="55">
         <f t="shared" si="39"/>
         <v>2.6157666398074673E-2</v>
       </c>
-      <c r="E92" s="56">
+      <c r="E92" s="55">
         <f t="shared" si="40"/>
         <v>2.5652817623557908E-2</v>
       </c>
-      <c r="F92" s="56">
+      <c r="F92" s="55">
         <f t="shared" si="41"/>
         <v>6.8629203061551403E-2</v>
       </c>
-      <c r="G92" s="56">
+      <c r="G92" s="55">
         <f t="shared" si="42"/>
         <v>0.6699019689329424</v>
       </c>
-      <c r="H92" s="51">
+      <c r="H92" s="50">
         <f t="shared" si="43"/>
         <v>3.204762753429935</v>
       </c>
-      <c r="I92" s="51">
+      <c r="I92" s="50">
         <f t="shared" si="44"/>
         <v>2.4691266760270261</v>
       </c>
-      <c r="K92" s="37"/>
+      <c r="K92" s="36"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="11">
         <v>9</v>
       </c>
-      <c r="B93" s="36">
+      <c r="B93" s="35">
         <f t="shared" si="37"/>
         <v>52692.691275067969</v>
       </c>
-      <c r="C93" s="36">
+      <c r="C93" s="35">
         <f t="shared" si="38"/>
         <v>63231.22953008156</v>
       </c>
-      <c r="D93" s="56">
+      <c r="D93" s="55">
         <f t="shared" si="39"/>
         <v>2.5824424473964859E-2</v>
       </c>
-      <c r="E93" s="56">
+      <c r="E93" s="55">
         <f t="shared" si="40"/>
         <v>2.5358659128890969E-2</v>
       </c>
-      <c r="F93" s="56">
+      <c r="F93" s="55">
         <f t="shared" si="41"/>
         <v>8.57522759653149E-2</v>
       </c>
-      <c r="G93" s="56">
+      <c r="G93" s="55">
         <f t="shared" si="42"/>
         <v>0.83812252265746989</v>
       </c>
-      <c r="H93" s="51">
+      <c r="H93" s="50">
         <f t="shared" si="43"/>
         <v>3.5139491438770154</v>
       </c>
-      <c r="I93" s="51">
+      <c r="I93" s="50">
         <f t="shared" si="44"/>
         <v>3.1249884493467048</v>
       </c>
-      <c r="K93" s="37"/>
+      <c r="K93" s="36"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A94" s="38">
+      <c r="A94" s="37">
         <v>10</v>
       </c>
-      <c r="B94" s="36">
+      <c r="B94" s="35">
         <f t="shared" si="37"/>
         <v>58547.434750075525</v>
       </c>
-      <c r="C94" s="36">
+      <c r="C94" s="35">
         <f t="shared" si="38"/>
         <v>70256.921700090621</v>
       </c>
-      <c r="D94" s="56">
+      <c r="D94" s="55">
         <f t="shared" si="39"/>
         <v>2.5548135310566166E-2</v>
       </c>
-      <c r="E94" s="56">
+      <c r="E94" s="55">
         <f t="shared" si="40"/>
         <v>2.5115298425681609E-2</v>
       </c>
-      <c r="F94" s="56">
+      <c r="F94" s="55">
         <f t="shared" si="41"/>
         <v>0.1047343623011591</v>
       </c>
-      <c r="G94" s="51">
+      <c r="G94" s="50">
         <f t="shared" si="42"/>
         <v>1.0247892229981916</v>
       </c>
-      <c r="H94" s="60">
+      <c r="H94" s="59">
         <f t="shared" si="43"/>
         <v>3.8580104312922283</v>
       </c>
-      <c r="I94" s="51">
+      <c r="I94" s="50">
         <f t="shared" si="44"/>
         <v>3.8580104312922283</v>
       </c>
-      <c r="K94" s="37"/>
+      <c r="K94" s="36"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="11">
         <v>11</v>
       </c>
-      <c r="B95" s="36">
+      <c r="B95" s="35">
         <f t="shared" si="37"/>
         <v>64402.178225083073</v>
       </c>
-      <c r="C95" s="36">
+      <c r="C95" s="35">
         <f t="shared" si="38"/>
         <v>77282.613870099696</v>
       </c>
-      <c r="D95" s="56">
+      <c r="D95" s="55">
         <f t="shared" si="39"/>
         <v>2.5314967129198923E-2</v>
       </c>
-      <c r="E95" s="56">
+      <c r="E95" s="55">
         <f t="shared" si="40"/>
         <v>2.4910312727500619E-2</v>
       </c>
-      <c r="F95" s="56">
+      <c r="F95" s="55">
         <f t="shared" si="41"/>
         <v>0.12557197451527682</v>
       </c>
-      <c r="G95" s="51">
+      <c r="G95" s="50">
         <f t="shared" si="42"/>
         <v>1.2298743859738575</v>
       </c>
-      <c r="H95" s="51">
+      <c r="H95" s="50">
         <f t="shared" si="43"/>
         <v>4.2369154441405161</v>
       </c>
-      <c r="I95" s="51">
+      <c r="I95" s="50">
         <f t="shared" si="44"/>
         <v>4.6681926218635965</v>
       </c>
-      <c r="K95" s="37"/>
+      <c r="K95" s="36"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="11">
         <v>12</v>
       </c>
-      <c r="B96" s="36">
+      <c r="B96" s="35">
         <f t="shared" si="37"/>
         <v>70256.921700090621</v>
       </c>
-      <c r="C96" s="36">
+      <c r="C96" s="35">
         <f t="shared" si="38"/>
         <v>84308.306040108757</v>
       </c>
-      <c r="D96" s="56">
+      <c r="D96" s="55">
         <f t="shared" si="39"/>
         <v>2.5115298425681609E-2</v>
       </c>
-      <c r="E96" s="56">
+      <c r="E96" s="55">
         <f t="shared" si="40"/>
         <v>2.4735078652284546E-2</v>
       </c>
-      <c r="F96" s="56">
+      <c r="F96" s="55">
         <f t="shared" si="41"/>
         <v>0.14826232971617359</v>
       </c>
-      <c r="G96" s="51">
+      <c r="G96" s="50">
         <f t="shared" si="42"/>
         <v>1.453355954951099</v>
       </c>
-      <c r="H96" s="51">
+      <c r="H96" s="50">
         <f t="shared" si="43"/>
         <v>4.6506393428970156</v>
       </c>
-      <c r="I96" s="51">
+      <c r="I96" s="50">
         <f t="shared" si="44"/>
         <v>5.555535021060809</v>
       </c>
-      <c r="K96" s="37"/>
+      <c r="K96" s="36"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="11">
         <v>13</v>
       </c>
-      <c r="B97" s="36">
+      <c r="B97" s="35">
         <f t="shared" si="37"/>
         <v>76111.665175098169</v>
       </c>
-      <c r="C97" s="36">
+      <c r="C97" s="35">
         <f t="shared" si="38"/>
         <v>91333.998210117803</v>
       </c>
-      <c r="D97" s="56">
+      <c r="D97" s="55">
         <f t="shared" si="39"/>
         <v>2.4942213741927205E-2</v>
       </c>
-      <c r="E97" s="56">
+      <c r="E97" s="55">
         <f t="shared" si="40"/>
         <v>2.4583410261233431E-2</v>
       </c>
-      <c r="F97" s="56">
+      <c r="F97" s="55">
         <f t="shared" si="41"/>
         <v>0.17280316249756403</v>
       </c>
-      <c r="G97" s="51">
+      <c r="G97" s="50">
         <f t="shared" si="42"/>
         <v>1.695215990262547</v>
       </c>
-      <c r="H97" s="51">
+      <c r="H97" s="50">
         <f t="shared" si="43"/>
         <v>5.099161922488074</v>
       </c>
-      <c r="I97" s="51">
+      <c r="I97" s="50">
         <f t="shared" si="44"/>
         <v>6.5200376288838653</v>
       </c>
-      <c r="K97" s="37"/>
+      <c r="K97" s="36"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="11">
         <v>14</v>
       </c>
-      <c r="B98" s="36">
+      <c r="B98" s="35">
         <f t="shared" si="37"/>
         <v>81966.408650105732</v>
       </c>
-      <c r="C98" s="36">
+      <c r="C98" s="35">
         <f t="shared" si="38"/>
         <v>98359.690380126864</v>
       </c>
-      <c r="D98" s="56">
+      <c r="D98" s="55">
         <f t="shared" si="39"/>
         <v>2.4790605712953471E-2</v>
       </c>
-      <c r="E98" s="56">
+      <c r="E98" s="55">
         <f t="shared" si="40"/>
         <v>2.4450747337404773E-2</v>
       </c>
-      <c r="F98" s="56">
+      <c r="F98" s="55">
         <f t="shared" si="41"/>
         <v>0.19919259733568023</v>
       </c>
-      <c r="G98" s="51">
+      <c r="G98" s="50">
         <f t="shared" si="42"/>
         <v>1.9554396449617522</v>
       </c>
-      <c r="H98" s="51">
+      <c r="H98" s="50">
         <f t="shared" si="43"/>
         <v>5.5824664604434719</v>
       </c>
-      <c r="I98" s="51">
+      <c r="I98" s="50">
         <f t="shared" si="44"/>
         <v>7.5617004453327672</v>
       </c>
-      <c r="K98" s="37"/>
+      <c r="K98" s="36"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" s="39" t="s">
+      <c r="A105" s="38" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A106" s="40" t="s">
+      <c r="A106" s="39" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" s="41" t="s">
+      <c r="A107" s="40" t="s">
         <v>117</v>
       </c>
     </row>
@@ -13208,17 +13205,17 @@
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="39" t="s">
+      <c r="A126" s="38" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="40" t="s">
+      <c r="A127" s="39" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="41" t="s">
+      <c r="A128" s="40" t="s">
         <v>86</v>
       </c>
     </row>
@@ -13229,17 +13226,17 @@
     </row>
     <row r="144" spans="1:1" ht="69.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="42" t="s">
+      <c r="A145" s="41" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="43" t="s">
+      <c r="A146" s="42" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="41"/>
+      <c r="A147" s="40"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B150" s="9" t="s">
@@ -13265,10 +13262,10 @@
       <c r="A153" s="3">
         <v>1200</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="61">
         <v>8.1999999999999993</v>
       </c>
-      <c r="C153" s="63">
+      <c r="C153" s="62">
         <v>3.25</v>
       </c>
     </row>
@@ -13276,21 +13273,21 @@
       <c r="A154" s="3">
         <v>1500</v>
       </c>
-      <c r="B154" s="62">
+      <c r="B154" s="61">
         <v>11.85</v>
       </c>
-      <c r="C154" s="63">
+      <c r="C154" s="62">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="42" t="s">
+      <c r="A160" s="41" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="40" t="s">
+      <c r="A161" s="39" t="s">
         <v>45</v>
       </c>
     </row>
@@ -13314,15 +13311,15 @@
       <c r="A166" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B166" s="44">
+      <c r="B166" s="43">
         <f>Qpv</f>
         <v>10</v>
       </c>
-      <c r="C166" s="45">
+      <c r="C166" s="44">
         <f>Hpv</f>
         <v>3.8580104312922283</v>
       </c>
-      <c r="D166" s="46"/>
+      <c r="D166" s="45"/>
       <c r="E166" s="9"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -13366,38 +13363,38 @@
       <c r="A171" s="9">
         <v>1200</v>
       </c>
-      <c r="B171" s="62">
+      <c r="B171" s="61">
         <v>9</v>
       </c>
-      <c r="C171" s="63">
+      <c r="C171" s="62">
         <v>3.1</v>
       </c>
-      <c r="D171" s="64">
+      <c r="D171" s="63">
         <f>A171*(B166/B171)</f>
         <v>1333.3333333333335</v>
       </c>
-      <c r="E171" s="64">
+      <c r="E171" s="63">
         <f>A171*SQRT(C166/C171)</f>
         <v>1338.6964074464149</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
-        <v>1200</v>
-      </c>
-      <c r="B172" s="62">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C172" s="63">
-        <v>3.25</v>
-      </c>
-      <c r="D172" s="64">
+        <v>1500</v>
+      </c>
+      <c r="B172" s="61">
+        <v>11.2</v>
+      </c>
+      <c r="C172" s="62">
+        <v>4.8</v>
+      </c>
+      <c r="D172" s="63">
         <f>A172*(B166/B172)</f>
-        <v>1463.4146341463418</v>
-      </c>
-      <c r="E172" s="64">
+        <v>1339.2857142857144</v>
+      </c>
+      <c r="E172" s="63">
         <f>A172*SQRT(C166/C172)</f>
-        <v>1307.4384846315459</v>
+        <v>1344.7833987926206</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -13408,17 +13405,17 @@
     </row>
     <row r="175" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="42" t="s">
+      <c r="A176" s="41" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="40" t="s">
+      <c r="A177" s="39" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="41" t="s">
+      <c r="A178" s="40" t="s">
         <v>86</v>
       </c>
     </row>
@@ -13448,7 +13445,7 @@
       <c r="L179" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="M179" s="32">
+      <c r="M179" s="31">
         <v>7000</v>
       </c>
       <c r="N179" s="3" t="s">
@@ -13483,7 +13480,7 @@
       <c r="L180" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="M180" s="47">
+      <c r="M180" s="46">
         <v>0.8</v>
       </c>
     </row>
@@ -13515,7 +13512,7 @@
       <c r="L181" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M181" s="47">
+      <c r="M181" s="46">
         <v>0.95</v>
       </c>
     </row>
@@ -13533,101 +13530,171 @@
       <c r="A183" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C183" s="48">
-        <v>3.1</v>
-      </c>
-      <c r="D183" s="65">
+      <c r="C183" s="62">
+        <f>C171*(E171/A171)^2</f>
+        <v>3.8580104312922274</v>
+      </c>
+      <c r="D183" s="64">
         <f>$B$166</f>
         <v>10</v>
       </c>
-      <c r="E183" s="48">
-        <v>9</v>
-      </c>
-      <c r="F183" s="49"/>
-      <c r="G183" s="17"/>
-      <c r="H183" s="17"/>
-      <c r="I183" s="17"/>
-      <c r="J183" s="17"/>
+      <c r="E183" s="64">
+        <v>10</v>
+      </c>
+      <c r="F183" s="48">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="G183" s="49">
+        <f>Densitet*Tyngdacc*(D183/3600)*C183</f>
+        <v>104.94154884105832</v>
+      </c>
+      <c r="H183" s="49">
+        <f>(Densitet*Tyngdacc*(E183/3600)*C183)/F183</f>
+        <v>248.67665602146522</v>
+      </c>
+      <c r="I183" s="49">
+        <f>H183/(Verkningsgrad_elmotor*Verkningsgrad_frekvensomriktare)</f>
+        <v>327.20612634403318</v>
+      </c>
+      <c r="J183" s="63">
+        <f>(I183*Årlig_drifttid)/1000</f>
+        <v>2290.4428844082322</v>
+      </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C184" s="48">
-        <v>4.8</v>
-      </c>
-      <c r="D184" s="65">
-        <f t="shared" ref="D184:D187" si="45">$B$166</f>
+      <c r="C184" s="62">
+        <f>C172*(E172/A172)^2</f>
+        <v>3.8580104312922292</v>
+      </c>
+      <c r="D184" s="64">
+        <f t="shared" ref="D184:D185" si="45">$B$166</f>
         <v>10</v>
       </c>
-      <c r="E184" s="48">
-        <v>11.2</v>
-      </c>
-      <c r="F184" s="49"/>
-      <c r="G184" s="17"/>
-      <c r="H184" s="17"/>
-      <c r="I184" s="17"/>
-      <c r="J184" s="17"/>
+      <c r="E184" s="64">
+        <v>10</v>
+      </c>
+      <c r="F184" s="48">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="G184" s="49">
+        <f>Densitet*Tyngdacc*(D184/3600)*C184</f>
+        <v>104.94154884105838</v>
+      </c>
+      <c r="H184" s="49">
+        <f>(Densitet*Tyngdacc*(E184/3600)*C184)/F184</f>
+        <v>226.65561304764228</v>
+      </c>
+      <c r="I184" s="49">
+        <f>H184/(Verkningsgrad_elmotor*Verkningsgrad_frekvensomriktare)</f>
+        <v>298.23106979952928</v>
+      </c>
+      <c r="J184" s="63">
+        <f>(I184*Årlig_drifttid)/1000</f>
+        <v>2087.6174885967052</v>
+      </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C185" s="48">
+      <c r="C185" s="47">
         <v>5.15</v>
       </c>
-      <c r="D185" s="65">
+      <c r="D185" s="64">
         <f t="shared" si="45"/>
         <v>10</v>
       </c>
-      <c r="E185" s="48">
+      <c r="E185" s="64">
         <v>10</v>
       </c>
-      <c r="F185" s="49"/>
-      <c r="G185" s="17"/>
-      <c r="H185" s="17"/>
-      <c r="I185" s="17"/>
-      <c r="J185" s="17"/>
+      <c r="F185" s="48">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="G185" s="49">
+        <f>Densitet*Tyngdacc*(D185/3600)*C185</f>
+        <v>140.08489250000002</v>
+      </c>
+      <c r="H185" s="49">
+        <f>(Densitet*Tyngdacc*(E185/3600)*C185)/F185</f>
+        <v>302.55916306695468</v>
+      </c>
+      <c r="I185" s="49">
+        <f>H185/Verkningsgrad_elmotor</f>
+        <v>378.19895383369334</v>
+      </c>
+      <c r="J185" s="63">
+        <f>(I185*Årlig_drifttid)/1000</f>
+        <v>2647.3926768358533</v>
+      </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C186" s="48">
+      <c r="C186" s="47">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D186" s="65">
-        <f t="shared" si="45"/>
+      <c r="D186" s="64">
         <v>10</v>
       </c>
-      <c r="E186" s="48">
+      <c r="E186" s="64">
         <v>11.9</v>
       </c>
-      <c r="F186" s="49"/>
-      <c r="G186" s="17"/>
-      <c r="H186" s="17"/>
-      <c r="I186" s="17"/>
-      <c r="J186" s="17"/>
+      <c r="F186" s="48">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="G186" s="49">
+        <f>Densitet*Tyngdacc*(D186/3600)*C186</f>
+        <v>125.12437</v>
+      </c>
+      <c r="H186" s="49">
+        <f>(Densitet*Tyngdacc*(E186/3600)*C186)/F186</f>
+        <v>318.83940107066383</v>
+      </c>
+      <c r="I186" s="49">
+        <f>H186/Verkningsgrad_elmotor</f>
+        <v>398.54925133832978</v>
+      </c>
+      <c r="J186" s="63">
+        <f>(I186*Årlig_drifttid)/1000</f>
+        <v>2789.8447593683081</v>
+      </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C187" s="48">
+      <c r="C187" s="47">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D187" s="65">
-        <f t="shared" si="45"/>
-        <v>10</v>
-      </c>
-      <c r="E187" s="48">
+      <c r="D187" s="64">
         <v>11.9</v>
       </c>
-      <c r="F187" s="49"/>
-      <c r="G187" s="17"/>
-      <c r="H187" s="17"/>
-      <c r="I187" s="17"/>
-      <c r="J187" s="17"/>
+      <c r="E187" s="64">
+        <v>11.9</v>
+      </c>
+      <c r="F187" s="48">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="G187" s="49">
+        <f>Densitet*Tyngdacc*(D187/3600)*C187</f>
+        <v>148.89800030000001</v>
+      </c>
+      <c r="H187" s="49">
+        <f>(Densitet*Tyngdacc*(E187/3600)*C187)/F187</f>
+        <v>318.83940107066383</v>
+      </c>
+      <c r="I187" s="49">
+        <f>H187/Verkningsgrad_elmotor</f>
+        <v>398.54925133832978</v>
+      </c>
+      <c r="J187" s="63">
+        <f>(I187*(B166/E187)*Årlig_drifttid)/1000</f>
+        <v>2344.4073608137046</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
+++ b/ET2/Grupp5_Emil-P_ Johan-H_2026-05-21.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5112D32-B519-455D-9B94-05834A59BB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C42EC2-3F64-40A2-9D51-896B23422089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34605" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
     <numFmt numFmtId="169" formatCode="0.0000000"/>
     <numFmt numFmtId="170" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -682,8 +682,22 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -720,6 +734,16 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -754,11 +778,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -910,8 +936,16 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="7" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="8" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -13591,7 +13625,7 @@
         <f>H184/(Verkningsgrad_elmotor*Verkningsgrad_frekvensomriktare)</f>
         <v>298.23106979952928</v>
       </c>
-      <c r="J184" s="63">
+      <c r="J184" s="65">
         <f>(I184*Årlig_drifttid)/1000</f>
         <v>2087.6174885967052</v>
       </c>
@@ -13658,7 +13692,7 @@
         <f>H186/Verkningsgrad_elmotor</f>
         <v>398.54925133832978</v>
       </c>
-      <c r="J186" s="63">
+      <c r="J186" s="66">
         <f>(I186*Årlig_drifttid)/1000</f>
         <v>2789.8447593683081</v>
       </c>
